--- a/doc/VM ARPIA.xlsx
+++ b/doc/VM ARPIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ultron\domingos\Projetos\ARPIA\alpha\0.01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DomingosJoséPereiraP\projetos\arpiavm\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0DE575-A67F-4905-B2A8-65930DC2A626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE0994D-36E9-4FF5-A918-9E7A1A14C0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="281">
   <si>
     <t>MOV  AX, 14h</t>
   </si>
@@ -227,9 +227,6 @@
   </si>
   <si>
     <t>RST</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>bits</t>
@@ -884,7 +881,10 @@
     <t>Watchdog Counter</t>
   </si>
   <si>
-    <t>HALT</t>
+    <t>SPARE_1ST</t>
+  </si>
+  <si>
+    <t>SPARE_LAST</t>
   </si>
 </sst>
 </file>
@@ -900,7 +900,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -910,6 +910,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA8ADC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1409,7 +1445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1425,16 +1461,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1464,9 +1494,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1486,6 +1513,57 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1533,13 +1611,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1548,13 +1644,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1566,10 +1662,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1602,6 +1710,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFDA8ADC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1887,23 +2000,23 @@
     <col min="3" max="3" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="83.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="83.28515625" style="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="26" t="s">
-        <v>160</v>
+      <c r="B1" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="D1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2">
         <v>0</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>161</v>
+      <c r="C2" s="23" t="s">
+        <v>160</v>
       </c>
       <c r="D2" t="s">
         <v>0</v>
@@ -1913,8 +2026,8 @@
       <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>95</v>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="D3" t="s">
         <v>2</v>
@@ -1924,8 +2037,8 @@
       <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>162</v>
+      <c r="C4" s="23" t="s">
+        <v>161</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -1935,8 +2048,8 @@
       <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>163</v>
+      <c r="C5" s="23" t="s">
+        <v>162</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -1944,25 +2057,25 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" t="s">
         <v>158</v>
       </c>
-      <c r="D7" t="s">
-        <v>159</v>
-      </c>
       <c r="E7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>96</v>
+      <c r="G7" s="23" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1976,16 +2089,16 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>241</v>
+      <c r="G8" s="23" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1999,16 +2112,16 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E9" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="26" t="s">
-        <v>242</v>
+      <c r="G9" s="23" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2022,16 +2135,16 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>261</v>
+      <c r="G10" s="23" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2045,16 +2158,16 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="26" t="s">
-        <v>262</v>
+      <c r="G11" s="23" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2068,16 +2181,16 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>243</v>
+      <c r="G12" s="23" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2091,16 +2204,16 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="26" t="s">
-        <v>244</v>
+      <c r="G13" s="23" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2114,16 +2227,16 @@
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="26" t="s">
-        <v>263</v>
+      <c r="G14" s="23" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2137,16 +2250,16 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
-      </c>
-      <c r="E15" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="26" t="s">
-        <v>264</v>
+      <c r="G15" s="23" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2160,16 +2273,16 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="26" t="s">
-        <v>265</v>
+      <c r="G16" s="23" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2183,16 +2296,16 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>174</v>
-      </c>
-      <c r="E17" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="26" t="s">
-        <v>245</v>
+      <c r="G17" s="23" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2206,16 +2319,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E18" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="26" t="s">
-        <v>266</v>
+      <c r="G18" s="23" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2229,16 +2342,16 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E19" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="E19" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F19" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="26" t="s">
-        <v>253</v>
+      <c r="G19" s="23" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2252,16 +2365,16 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>177</v>
-      </c>
-      <c r="E20" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="26" t="s">
-        <v>254</v>
+      <c r="G20" s="23" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2275,16 +2388,16 @@
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>178</v>
-      </c>
-      <c r="E21" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G21" s="26" t="s">
-        <v>255</v>
+      <c r="G21" s="23" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2298,16 +2411,16 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
-      </c>
-      <c r="E22" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="26" t="s">
-        <v>256</v>
+      <c r="G22" s="23" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2321,16 +2434,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E23" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G23" s="26" t="s">
-        <v>257</v>
+      <c r="G23" s="23" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2344,16 +2457,16 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
-      </c>
-      <c r="E24" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="26" t="s">
-        <v>258</v>
+      <c r="G24" s="23" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2367,16 +2480,16 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
-      </c>
-      <c r="E25" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="E25" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="26" t="s">
-        <v>259</v>
+      <c r="G25" s="23" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2384,22 +2497,22 @@
         <v>18</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C26" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="25" t="s">
+      <c r="F26" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="26" t="s">
-        <v>260</v>
+      <c r="G26" s="23" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2413,14 +2526,14 @@
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>184</v>
-      </c>
-      <c r="E28" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="25"/>
-      <c r="G28" s="26" t="s">
-        <v>267</v>
+      <c r="F28" s="22"/>
+      <c r="G28" s="23" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2434,14 +2547,14 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
-      </c>
-      <c r="E29" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F29" s="25"/>
-      <c r="G29" s="26" t="s">
-        <v>268</v>
+      <c r="F29" s="22"/>
+      <c r="G29" s="23" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2455,13 +2568,13 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E30" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="E30" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="G30" s="26" t="s">
-        <v>246</v>
+      <c r="G30" s="23" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2475,13 +2588,13 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E31" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="G31" s="26" t="s">
-        <v>247</v>
+      <c r="G31" s="23" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2495,14 +2608,14 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>188</v>
-      </c>
-      <c r="E32" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E32" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="25"/>
-      <c r="G32" s="26" t="s">
-        <v>240</v>
+      <c r="F32" s="22"/>
+      <c r="G32" s="23" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2512,17 +2625,17 @@
       <c r="B33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>192</v>
-      </c>
-      <c r="E33" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="26" t="s">
-        <v>269</v>
+      <c r="G33" s="23" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2532,17 +2645,17 @@
       <c r="B34" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>191</v>
-      </c>
-      <c r="E34" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G34" s="26" t="s">
-        <v>270</v>
+      <c r="G34" s="23" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2552,17 +2665,17 @@
       <c r="B35" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>189</v>
-      </c>
-      <c r="E35" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G35" s="26" t="s">
-        <v>236</v>
+      <c r="G35" s="23" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2572,17 +2685,17 @@
       <c r="B36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>190</v>
-      </c>
-      <c r="E36" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="E36" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="26" t="s">
-        <v>237</v>
+      <c r="G36" s="23" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2592,17 +2705,17 @@
       <c r="B37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>193</v>
-      </c>
-      <c r="E37" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="E37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G37" s="26" t="s">
-        <v>238</v>
+      <c r="G37" s="23" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2612,17 +2725,17 @@
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G38" s="26" t="s">
-        <v>239</v>
+      <c r="G38" s="23" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2630,19 +2743,19 @@
         <v>18</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C39" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>195</v>
-      </c>
-      <c r="E39" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G39" s="26" t="s">
-        <v>234</v>
+      <c r="G39" s="23" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2650,19 +2763,19 @@
         <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>196</v>
-      </c>
-      <c r="E40" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E40" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G40" s="26" t="s">
-        <v>235</v>
+      <c r="G40" s="23" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2672,17 +2785,17 @@
       <c r="B41" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>197</v>
-      </c>
-      <c r="E41" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="E41" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G41" s="26" t="s">
-        <v>233</v>
+      <c r="G41" s="23" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2692,17 +2805,17 @@
       <c r="B42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>198</v>
-      </c>
-      <c r="E42" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E42" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G42" s="26" t="s">
-        <v>232</v>
+      <c r="G42" s="23" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2712,17 +2825,17 @@
       <c r="B43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="C43" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>199</v>
-      </c>
-      <c r="E43" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="26" t="s">
-        <v>231</v>
+      <c r="G43" s="23" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2732,17 +2845,17 @@
       <c r="B44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="C44" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>226</v>
-      </c>
-      <c r="E44" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="E44" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G44" s="26" t="s">
-        <v>248</v>
+      <c r="G44" s="23" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2750,19 +2863,19 @@
         <v>18</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C45" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>211</v>
-      </c>
-      <c r="E45" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="E45" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G45" s="26" t="s">
-        <v>224</v>
+      <c r="G45" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2770,19 +2883,19 @@
         <v>18</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C46" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>228</v>
-      </c>
-      <c r="E46" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E46" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G46" s="26" t="s">
-        <v>249</v>
+      <c r="G46" s="23" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2790,19 +2903,19 @@
         <v>18</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C47" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="22" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>200</v>
-      </c>
-      <c r="E47" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G47" s="26" t="s">
-        <v>222</v>
+      <c r="G47" s="23" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2810,13 +2923,13 @@
         <v>18</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D49" t="s">
-        <v>229</v>
-      </c>
-      <c r="G49" s="26" t="s">
-        <v>250</v>
+        <v>228</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2824,13 +2937,13 @@
         <v>18</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D50" t="s">
-        <v>230</v>
-      </c>
-      <c r="G50" s="26" t="s">
-        <v>251</v>
+        <v>229</v>
+      </c>
+      <c r="G50" s="23" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2838,15 +2951,15 @@
         <v>18</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C51" s="25"/>
+        <v>147</v>
+      </c>
+      <c r="C51" s="22"/>
       <c r="D51" t="s">
-        <v>201</v>
-      </c>
-      <c r="E51" s="25"/>
-      <c r="G51" s="26" t="s">
-        <v>221</v>
+        <v>200</v>
+      </c>
+      <c r="E51" s="22"/>
+      <c r="G51" s="23" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2854,15 +2967,15 @@
         <v>18</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C52" s="25"/>
+        <v>148</v>
+      </c>
+      <c r="C52" s="22"/>
       <c r="D52" t="s">
-        <v>202</v>
-      </c>
-      <c r="E52" s="25"/>
-      <c r="G52" s="26" t="s">
-        <v>220</v>
+        <v>201</v>
+      </c>
+      <c r="E52" s="22"/>
+      <c r="G52" s="23" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2873,10 +2986,10 @@
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>203</v>
-      </c>
-      <c r="G53" s="26" t="s">
-        <v>252</v>
+        <v>202</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2884,13 +2997,13 @@
         <v>18</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" t="s">
-        <v>227</v>
-      </c>
-      <c r="G54" s="26" t="s">
-        <v>252</v>
+        <v>226</v>
+      </c>
+      <c r="G54" s="23" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,13 +3011,13 @@
         <v>18</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D55" t="s">
-        <v>204</v>
-      </c>
-      <c r="G55" s="26" t="s">
-        <v>218</v>
+        <v>203</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2912,13 +3025,13 @@
         <v>61</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D56" t="s">
-        <v>205</v>
-      </c>
-      <c r="G56" s="26" t="s">
-        <v>219</v>
+        <v>204</v>
+      </c>
+      <c r="G56" s="23" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2929,10 +3042,10 @@
         <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
-      </c>
-      <c r="G57" s="26" t="s">
-        <v>217</v>
+        <v>140</v>
+      </c>
+      <c r="G57" s="23" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2940,13 +3053,13 @@
         <v>18</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D58" t="s">
-        <v>206</v>
-      </c>
-      <c r="G58" s="26" t="s">
-        <v>216</v>
+        <v>205</v>
+      </c>
+      <c r="G58" s="23" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2954,13 +3067,13 @@
         <v>18</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D59" t="s">
-        <v>207</v>
-      </c>
-      <c r="G59" s="26" t="s">
-        <v>215</v>
+        <v>206</v>
+      </c>
+      <c r="G59" s="23" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2968,13 +3081,13 @@
         <v>18</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D60" t="s">
-        <v>208</v>
-      </c>
-      <c r="G60" s="26" t="s">
-        <v>223</v>
+        <v>207</v>
+      </c>
+      <c r="G60" s="23" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2982,13 +3095,13 @@
         <v>18</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D61" t="s">
-        <v>209</v>
-      </c>
-      <c r="G61" s="26" t="s">
-        <v>214</v>
+        <v>208</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2996,13 +3109,13 @@
         <v>18</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D62" t="s">
-        <v>210</v>
-      </c>
-      <c r="G62" s="26" t="s">
-        <v>225</v>
+        <v>209</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,10 +3126,10 @@
         <v>41</v>
       </c>
       <c r="D63" t="s">
+        <v>211</v>
+      </c>
+      <c r="G63" s="23" t="s">
         <v>212</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -3030,9 +3143,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="17" width="4.5703125" customWidth="1"/>
     <col min="18" max="18" width="3.140625" style="6" customWidth="1"/>
     <col min="19" max="19" width="3.140625" customWidth="1"/>
@@ -3041,18 +3155,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B1" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
+      <c r="B1" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
       <c r="O1" s="6"/>
       <c r="R1"/>
       <c r="Z1" s="2"/>
@@ -3065,16 +3179,16 @@
       <c r="C2" s="4">
         <v>0</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
+      <c r="D2" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
       <c r="M2" s="1"/>
       <c r="O2" s="6"/>
       <c r="R2"/>
@@ -3088,16 +3202,16 @@
       <c r="C3" s="4">
         <v>1</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
+      <c r="D3" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
       <c r="O3" s="6"/>
       <c r="R3"/>
       <c r="Z3" s="2"/>
@@ -3110,16 +3224,16 @@
       <c r="C4" s="4">
         <v>0</v>
       </c>
-      <c r="D4" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
+      <c r="D4" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
       <c r="M4" s="1"/>
       <c r="O4" s="6"/>
       <c r="R4"/>
@@ -3133,16 +3247,16 @@
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+      <c r="D5" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
       <c r="O5" s="6"/>
       <c r="R5"/>
       <c r="Z5" s="2"/>
@@ -3155,58 +3269,58 @@
       <c r="AC6"/>
     </row>
     <row r="7" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B7" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
+      <c r="B7" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
       <c r="O7" s="6"/>
       <c r="R7"/>
       <c r="Z7" s="2"/>
       <c r="AC7"/>
     </row>
     <row r="8" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B8" s="46">
-        <v>0</v>
-      </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
+      <c r="B8" s="66">
+        <v>0</v>
+      </c>
+      <c r="C8" s="67"/>
+      <c r="D8" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
       <c r="O8" s="6"/>
       <c r="R8"/>
       <c r="Z8" s="2"/>
       <c r="AC8"/>
     </row>
     <row r="9" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B9" s="46">
-        <v>1</v>
-      </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
+      <c r="B9" s="66">
+        <v>1</v>
+      </c>
+      <c r="C9" s="67"/>
+      <c r="D9" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
       <c r="O9" s="6"/>
       <c r="R9"/>
       <c r="Z9" s="2"/>
@@ -3219,205 +3333,205 @@
       <c r="AC10"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+      <c r="AC11"/>
+    </row>
+    <row r="12" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B12" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="44"/>
+      <c r="AC12"/>
+    </row>
+    <row r="13" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AC11"/>
-    </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AC12"/>
-    </row>
-    <row r="13" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="45"/>
+      <c r="U13" s="45"/>
+      <c r="V13" s="45"/>
+      <c r="W13" s="45"/>
+      <c r="X13" s="45"/>
+      <c r="Y13" s="45"/>
+      <c r="Z13" s="45"/>
       <c r="AC13"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="31"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="31"/>
-      <c r="Z14" s="31"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="45"/>
+      <c r="T14" s="45"/>
+      <c r="U14" s="45"/>
+      <c r="V14" s="45"/>
+      <c r="W14" s="45"/>
+      <c r="X14" s="45"/>
+      <c r="Y14" s="45"/>
+      <c r="Z14" s="45"/>
       <c r="AC14"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="31"/>
-      <c r="W15" s="31"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="31"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="45"/>
+      <c r="R15" s="45"/>
+      <c r="S15" s="45"/>
+      <c r="T15" s="45"/>
+      <c r="U15" s="45"/>
+      <c r="V15" s="45"/>
+      <c r="W15" s="45"/>
+      <c r="X15" s="45"/>
+      <c r="Y15" s="45"/>
+      <c r="Z15" s="45"/>
       <c r="AC15"/>
     </row>
     <row r="16" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="45"/>
+      <c r="R16" s="45"/>
+      <c r="S16" s="45"/>
+      <c r="T16" s="45"/>
+      <c r="U16" s="45"/>
+      <c r="V16" s="45"/>
+      <c r="W16" s="45"/>
+      <c r="X16" s="45"/>
+      <c r="Y16" s="45"/>
+      <c r="Z16" s="45"/>
       <c r="AC16"/>
     </row>
     <row r="17" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="45"/>
+      <c r="R17" s="45"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="45"/>
+      <c r="U17" s="45"/>
+      <c r="V17" s="45"/>
+      <c r="W17" s="45"/>
+      <c r="X17" s="45"/>
+      <c r="Y17" s="45"/>
+      <c r="Z17" s="45"/>
       <c r="AC17"/>
     </row>
     <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
@@ -3535,71 +3649,71 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-      <c r="T20" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="U20" s="36"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="36"/>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="36"/>
+      <c r="T20" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="U20" s="50"/>
+      <c r="V20" s="50"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="50"/>
+      <c r="Z20" s="50"/>
+      <c r="AA20" s="50"/>
+      <c r="AB20" s="50"/>
+      <c r="AC20" s="50"/>
     </row>
     <row r="21" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11">
         <v>7</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="11">
         <v>6</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="11">
         <v>5</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="11">
         <v>4</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="11">
         <v>3</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="11">
         <v>2</v>
       </c>
-      <c r="H21" s="13">
-        <v>1</v>
-      </c>
-      <c r="I21" s="13">
-        <v>0</v>
-      </c>
-      <c r="J21" s="13">
+      <c r="H21" s="11">
+        <v>1</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0</v>
+      </c>
+      <c r="J21" s="11">
         <v>7</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="11">
         <v>6</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="11">
         <v>5</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="11">
         <v>4</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="11">
         <v>3</v>
       </c>
-      <c r="O21" s="13">
+      <c r="O21" s="11">
         <v>2</v>
       </c>
-      <c r="P21" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>0</v>
-      </c>
-      <c r="R21" s="14" t="s">
-        <v>65</v>
+      <c r="P21" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>0</v>
+      </c>
+      <c r="R21" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="T21" s="4" t="s">
         <v>12</v>
@@ -3613,46 +3727,46 @@
       <c r="AA21" s="4"/>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="8">
-        <v>0</v>
-      </c>
-      <c r="C22" s="8">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32" t="s">
+      <c r="B22" s="7">
+        <v>0</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32" t="s">
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="40" t="s">
+      <c r="O22" s="46"/>
+      <c r="P22" s="46"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="57" t="s">
         <v>53</v>
       </c>
       <c r="T22" s="4">
@@ -3697,7 +3811,7 @@
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="26" t="s">
         <v>7</v>
       </c>
       <c r="B23" s="5">
@@ -3712,41 +3826,41 @@
       <c r="E23" s="5">
         <v>1</v>
       </c>
-      <c r="F23" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28" t="s">
+      <c r="F23" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="48"/>
+      <c r="H23" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28" t="s">
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="39"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="58"/>
       <c r="T23" s="4">
-        <f t="shared" ref="T23:T79" si="2">U23*$E$19+V23*$I$19+W23*$M$19+X23</f>
+        <f t="shared" ref="T23:T78" si="2">U23*$E$19+V23*$I$19+W23*$M$19+X23</f>
         <v>4096</v>
       </c>
       <c r="U23" s="5">
-        <f t="shared" ref="U23:U79" si="3">IF(OR(E23=0,E23=1),E23,0)+IF(OR(D23=0,D23=1),D23*2,0)+IF(OR(C23=0,C23=1),C23*4,0)+IF(OR(B23=0,B23=1),B23*8,0)</f>
+        <f t="shared" ref="U23:U78" si="3">IF(OR(E23=0,E23=1),E23,0)+IF(OR(D23=0,D23=1),D23*2,0)+IF(OR(C23=0,C23=1),C23*4,0)+IF(OR(B23=0,B23=1),B23*8,0)</f>
         <v>1</v>
       </c>
       <c r="V23" s="5">
-        <f t="shared" ref="V23:V79" si="4">IF(OR(I23=0,I23=1),I23,0)+IF(OR(H23=0,H23=1),H23*2,0)+IF(OR(G23=0,G23=1),G23*4,0)+IF(OR(F23=0,F23=1),F23*8,0)</f>
+        <f t="shared" ref="V23:V78" si="4">IF(OR(I23=0,I23=1),I23,0)+IF(OR(H23=0,H23=1),H23*2,0)+IF(OR(G23=0,G23=1),G23*4,0)+IF(OR(F23=0,F23=1),F23*8,0)</f>
         <v>0</v>
       </c>
       <c r="W23" s="5">
-        <f t="shared" ref="W23:W79" si="5">IF(OR(M23=0,M23=1),M23,0)+IF(OR(L23=0,L23=1),L23*2,0)+IF(OR(K23=0,K23=1),K23*4,0)+IF(OR(J23=0,J23=1),J23*8,0)</f>
+        <f t="shared" ref="W23:W78" si="5">IF(OR(M23=0,M23=1),M23,0)+IF(OR(L23=0,L23=1),L23*2,0)+IF(OR(K23=0,K23=1),K23*4,0)+IF(OR(J23=0,J23=1),J23*8,0)</f>
         <v>0</v>
       </c>
       <c r="X23" s="5">
@@ -3754,28 +3868,28 @@
         <v>0</v>
       </c>
       <c r="Y23" s="5">
-        <f t="shared" ref="Y23:Y79" si="6">IF(U23&lt;10,U23,MID("ABCDEF",U23-9,1))</f>
+        <f t="shared" ref="Y23:Y78" si="6">IF(U23&lt;10,U23,MID("ABCDEF",U23-9,1))</f>
         <v>1</v>
       </c>
       <c r="Z23" s="5">
-        <f t="shared" ref="Z23:Z79" si="7">IF(V23&lt;10,V23,MID("ABCDEF",V23-9,1))</f>
+        <f t="shared" ref="Z23:Z78" si="7">IF(V23&lt;10,V23,MID("ABCDEF",V23-9,1))</f>
         <v>0</v>
       </c>
       <c r="AA23" s="5">
-        <f t="shared" ref="AA23:AA79" si="8">IF(W23&lt;10,W23,MID("ABCDEF",W23-9,1))</f>
+        <f t="shared" ref="AA23:AA78" si="8">IF(W23&lt;10,W23,MID("ABCDEF",W23-9,1))</f>
         <v>0</v>
       </c>
       <c r="AB23" s="5">
-        <f t="shared" ref="AB23:AB79" si="9">IF(X23&lt;10,X23,MID("ABCDEF",X23-9,1))</f>
+        <f t="shared" ref="AB23:AB78" si="9">IF(X23&lt;10,X23,MID("ABCDEF",X23-9,1))</f>
         <v>0</v>
       </c>
       <c r="AC23" s="4" t="str">
-        <f t="shared" ref="AC23:AC73" si="10">Y23 &amp; Z23 &amp; AA23 &amp; AB23</f>
+        <f t="shared" ref="AC23:AC72" si="10">Y23 &amp; Z23 &amp; AA23 &amp; AB23</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="26" t="s">
         <v>8</v>
       </c>
       <c r="B24" s="5">
@@ -3790,27 +3904,27 @@
       <c r="E24" s="5">
         <v>0</v>
       </c>
-      <c r="F24" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28" t="s">
+      <c r="F24" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="48"/>
+      <c r="H24" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28" t="s">
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O24" s="28"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="39"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="58"/>
       <c r="T24" s="4">
         <f t="shared" si="2"/>
         <v>8192</v>
@@ -3853,7 +3967,7 @@
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="5">
@@ -3868,27 +3982,27 @@
       <c r="E25" s="5">
         <v>1</v>
       </c>
-      <c r="F25" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G25" s="34"/>
-      <c r="H25" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28" t="s">
+      <c r="F25" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G25" s="48"/>
+      <c r="H25" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28" t="s">
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="39"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="58"/>
       <c r="T25" s="4">
         <f t="shared" si="2"/>
         <v>12288</v>
@@ -3931,7 +4045,7 @@
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="26" t="s">
         <v>13</v>
       </c>
       <c r="B26" s="5">
@@ -3946,27 +4060,27 @@
       <c r="E26" s="5">
         <v>0</v>
       </c>
-      <c r="F26" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28" t="s">
+      <c r="F26" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="48"/>
+      <c r="H26" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28" t="s">
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="39"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="58"/>
       <c r="T26" s="4">
         <f t="shared" si="2"/>
         <v>16384</v>
@@ -4009,7 +4123,7 @@
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B27" s="5">
@@ -4024,27 +4138,27 @@
       <c r="E27" s="5">
         <v>1</v>
       </c>
-      <c r="F27" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28" t="s">
+      <c r="F27" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" s="48"/>
+      <c r="H27" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28" t="s">
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="39"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="58"/>
       <c r="T27" s="4">
         <f t="shared" si="2"/>
         <v>20480</v>
@@ -4087,7 +4201,7 @@
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="26" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="5">
@@ -4102,27 +4216,27 @@
       <c r="E28" s="5">
         <v>0</v>
       </c>
-      <c r="F28" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G28" s="34"/>
-      <c r="H28" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28" t="s">
+      <c r="F28" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G28" s="48"/>
+      <c r="H28" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28" t="s">
+      <c r="K28" s="42"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="39"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="58"/>
       <c r="T28" s="4">
         <f t="shared" si="2"/>
         <v>24576</v>
@@ -4165,7 +4279,7 @@
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="26" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="5">
@@ -4180,27 +4294,27 @@
       <c r="E29" s="5">
         <v>1</v>
       </c>
-      <c r="F29" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28" t="s">
+      <c r="F29" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" s="48"/>
+      <c r="H29" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28" t="s">
+      <c r="K29" s="42"/>
+      <c r="L29" s="42"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="39"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="58"/>
       <c r="T29" s="4">
         <f t="shared" si="2"/>
         <v>28672</v>
@@ -4243,7 +4357,7 @@
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="26" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="5">
@@ -4258,27 +4372,27 @@
       <c r="E30" s="5">
         <v>0</v>
       </c>
-      <c r="F30" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G30" s="34"/>
-      <c r="H30" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28" t="s">
+      <c r="F30" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="48"/>
+      <c r="H30" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28" t="s">
+      <c r="K30" s="42"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="39"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="58"/>
       <c r="T30" s="4">
         <f t="shared" si="2"/>
         <v>32768</v>
@@ -4321,7 +4435,7 @@
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="26" t="s">
         <v>42</v>
       </c>
       <c r="B31" s="5">
@@ -4336,27 +4450,27 @@
       <c r="E31" s="5">
         <v>1</v>
       </c>
-      <c r="F31" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28" t="s">
+      <c r="F31" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G31" s="48"/>
+      <c r="H31" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28" t="s">
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="39"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="58"/>
       <c r="T31" s="4">
         <f t="shared" si="2"/>
         <v>36864</v>
@@ -4399,7 +4513,7 @@
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="26" t="s">
         <v>43</v>
       </c>
       <c r="B32" s="5">
@@ -4414,27 +4528,27 @@
       <c r="E32" s="5">
         <v>0</v>
       </c>
-      <c r="F32" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28" t="s">
+      <c r="F32" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G32" s="48"/>
+      <c r="H32" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28" t="s">
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="39"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="58"/>
       <c r="T32" s="4">
         <f t="shared" si="2"/>
         <v>40960</v>
@@ -4477,42 +4591,42 @@
       </c>
     </row>
     <row r="33" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="11">
-        <v>1</v>
-      </c>
-      <c r="C33" s="11">
-        <v>0</v>
-      </c>
-      <c r="D33" s="11">
-        <v>1</v>
-      </c>
-      <c r="E33" s="11">
-        <v>1</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29" t="s">
+      <c r="B33" s="9">
+        <v>1</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>1</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="G33" s="52"/>
+      <c r="H33" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29" t="s">
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="59"/>
       <c r="T33" s="4">
         <f t="shared" si="2"/>
         <v>45056</v>
@@ -4555,44 +4669,44 @@
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="8">
-        <v>1</v>
-      </c>
-      <c r="C34" s="8">
-        <v>1</v>
-      </c>
-      <c r="D34" s="8">
-        <v>0</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0</v>
-      </c>
-      <c r="F34" s="8">
-        <v>0</v>
-      </c>
-      <c r="G34" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="H34" s="32"/>
-      <c r="I34" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="J34" s="32" t="s">
+      <c r="B34" s="7">
+        <v>1</v>
+      </c>
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7">
+        <v>0</v>
+      </c>
+      <c r="G34" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="46"/>
+      <c r="I34" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="J34" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32" t="s">
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="O34" s="32"/>
-      <c r="P34" s="32"/>
-      <c r="Q34" s="32"/>
-      <c r="R34" s="40" t="s">
+      <c r="O34" s="46"/>
+      <c r="P34" s="46"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="60" t="s">
         <v>54</v>
       </c>
       <c r="T34" s="4">
@@ -4637,7 +4751,7 @@
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B35" s="5">
@@ -4655,26 +4769,26 @@
       <c r="F35" s="5">
         <v>1</v>
       </c>
-      <c r="G35" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="H35" s="28"/>
+      <c r="G35" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" s="42"/>
       <c r="I35" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="J35" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28" t="s">
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="39"/>
+      <c r="O35" s="42"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="61"/>
       <c r="T35" s="4">
         <f t="shared" si="2"/>
         <v>51200</v>
@@ -4717,7 +4831,7 @@
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="29" t="s">
         <v>38</v>
       </c>
       <c r="B36" s="5">
@@ -4735,26 +4849,26 @@
       <c r="F36" s="5">
         <v>0</v>
       </c>
-      <c r="G36" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="H36" s="28"/>
+      <c r="G36" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" s="42"/>
       <c r="I36" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="J36" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="J36" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28" t="s">
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="39"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="61"/>
       <c r="T36" s="4">
         <f t="shared" si="2"/>
         <v>53248</v>
@@ -4797,44 +4911,44 @@
       </c>
     </row>
     <row r="37" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="21">
-        <v>1</v>
-      </c>
-      <c r="C37" s="21">
-        <v>1</v>
-      </c>
-      <c r="D37" s="21">
-        <v>0</v>
-      </c>
-      <c r="E37" s="21">
-        <v>1</v>
-      </c>
-      <c r="F37" s="21">
-        <v>1</v>
-      </c>
-      <c r="G37" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="H37" s="35"/>
-      <c r="I37" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="J37" s="35" t="s">
+      <c r="B37" s="18">
+        <v>1</v>
+      </c>
+      <c r="C37" s="18">
+        <v>1</v>
+      </c>
+      <c r="D37" s="18">
+        <v>0</v>
+      </c>
+      <c r="E37" s="18">
+        <v>1</v>
+      </c>
+      <c r="F37" s="18">
+        <v>1</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="H37" s="49"/>
+      <c r="I37" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="J37" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="35"/>
-      <c r="N37" s="35" t="s">
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
+      <c r="N37" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="49"/>
+      <c r="P37" s="49"/>
+      <c r="Q37" s="49"/>
+      <c r="R37" s="62"/>
       <c r="T37" s="4">
         <f t="shared" si="2"/>
         <v>55296</v>
@@ -4877,46 +4991,46 @@
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="8">
-        <v>1</v>
-      </c>
-      <c r="C38" s="8">
-        <v>1</v>
-      </c>
-      <c r="D38" s="8">
-        <v>1</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0</v>
-      </c>
-      <c r="F38" s="8">
-        <v>0</v>
-      </c>
-      <c r="G38" s="8">
-        <v>0</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="J38" s="32" t="s">
+      <c r="B38" s="7">
+        <v>1</v>
+      </c>
+      <c r="C38" s="7">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7">
+        <v>0</v>
+      </c>
+      <c r="G38" s="7">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="J38" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
-      <c r="N38" s="32" t="s">
+      <c r="K38" s="46"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="O38" s="32"/>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="54" t="s">
+      <c r="O38" s="46"/>
+      <c r="P38" s="46"/>
+      <c r="Q38" s="54"/>
+      <c r="R38" s="74" t="s">
         <v>55</v>
       </c>
       <c r="T38" s="4">
@@ -4961,7 +5075,7 @@
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="32" t="s">
         <v>60</v>
       </c>
       <c r="B39" s="5">
@@ -4983,24 +5097,24 @@
         <v>1</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="J39" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="J39" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28" t="s">
+      <c r="K39" s="42"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="42"/>
+      <c r="N39" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="49"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="53"/>
+      <c r="R39" s="75"/>
       <c r="T39" s="4">
         <f t="shared" ref="T39:T40" si="11">U39*$E$19+V39*$I$19+W39*$M$19+X39</f>
         <v>58368</v>
@@ -5043,46 +5157,46 @@
       </c>
     </row>
     <row r="40" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="B40" s="11">
-        <v>1</v>
-      </c>
-      <c r="C40" s="11">
-        <v>1</v>
-      </c>
-      <c r="D40" s="11">
-        <v>1</v>
-      </c>
-      <c r="E40" s="11">
-        <v>0</v>
-      </c>
-      <c r="F40" s="11">
-        <v>1</v>
-      </c>
-      <c r="G40" s="11">
-        <v>0</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="J40" s="29" t="s">
+      <c r="A40" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" s="9">
+        <v>1</v>
+      </c>
+      <c r="C40" s="9">
+        <v>1</v>
+      </c>
+      <c r="D40" s="9">
+        <v>1</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="J40" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29" t="s">
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="42"/>
-      <c r="R40" s="55"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="43"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="76"/>
       <c r="T40" s="4">
         <f t="shared" si="11"/>
         <v>59392</v>
@@ -5125,50 +5239,50 @@
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="23">
-        <v>1</v>
-      </c>
-      <c r="C41" s="23">
-        <v>1</v>
-      </c>
-      <c r="D41" s="23">
-        <v>1</v>
-      </c>
-      <c r="E41" s="23">
-        <v>1</v>
-      </c>
-      <c r="F41" s="23">
-        <v>1</v>
-      </c>
-      <c r="G41" s="23">
-        <v>1</v>
-      </c>
-      <c r="H41" s="23">
-        <v>0</v>
-      </c>
-      <c r="I41" s="23">
-        <v>0</v>
-      </c>
-      <c r="J41" s="23">
-        <v>0</v>
-      </c>
-      <c r="K41" s="23">
-        <v>0</v>
-      </c>
-      <c r="L41" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="M41" s="41"/>
-      <c r="N41" s="41" t="s">
+      <c r="B41" s="20">
+        <v>1</v>
+      </c>
+      <c r="C41" s="20">
+        <v>1</v>
+      </c>
+      <c r="D41" s="20">
+        <v>1</v>
+      </c>
+      <c r="E41" s="20">
+        <v>1</v>
+      </c>
+      <c r="F41" s="20">
+        <v>1</v>
+      </c>
+      <c r="G41" s="20">
+        <v>1</v>
+      </c>
+      <c r="H41" s="20">
+        <v>0</v>
+      </c>
+      <c r="I41" s="20">
+        <v>0</v>
+      </c>
+      <c r="J41" s="20">
+        <v>0</v>
+      </c>
+      <c r="K41" s="20">
+        <v>0</v>
+      </c>
+      <c r="L41" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="O41" s="41"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="40" t="s">
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="77" t="s">
         <v>56</v>
       </c>
       <c r="T41" s="4">
@@ -5213,7 +5327,7 @@
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="35" t="s">
         <v>12</v>
       </c>
       <c r="B42" s="5">
@@ -5246,17 +5360,17 @@
       <c r="K42" s="5">
         <v>1</v>
       </c>
-      <c r="L42" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28" t="s">
+      <c r="L42" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="39"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="78"/>
       <c r="T42" s="4">
         <f t="shared" si="2"/>
         <v>64576</v>
@@ -5299,7 +5413,7 @@
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="35" t="s">
         <v>16</v>
       </c>
       <c r="B43" s="5">
@@ -5332,17 +5446,17 @@
       <c r="K43" s="5">
         <v>0</v>
       </c>
-      <c r="L43" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28" t="s">
+      <c r="L43" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="M43" s="42"/>
+      <c r="N43" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="39"/>
+      <c r="O43" s="42"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="78"/>
       <c r="T43" s="4">
         <f t="shared" si="2"/>
         <v>64640</v>
@@ -5385,7 +5499,7 @@
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B44" s="5">
@@ -5418,17 +5532,17 @@
       <c r="K44" s="5">
         <v>1</v>
       </c>
-      <c r="L44" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28" t="s">
+      <c r="L44" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="M44" s="42"/>
+      <c r="N44" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="39"/>
+      <c r="O44" s="42"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="78"/>
       <c r="T44" s="4">
         <f t="shared" si="2"/>
         <v>64704</v>
@@ -5471,50 +5585,50 @@
       </c>
     </row>
     <row r="45" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B45" s="21">
-        <v>1</v>
-      </c>
-      <c r="C45" s="21">
-        <v>1</v>
-      </c>
-      <c r="D45" s="21">
-        <v>1</v>
-      </c>
-      <c r="E45" s="21">
-        <v>1</v>
-      </c>
-      <c r="F45" s="21">
-        <v>1</v>
-      </c>
-      <c r="G45" s="21">
-        <v>1</v>
-      </c>
-      <c r="H45" s="21">
-        <v>0</v>
-      </c>
-      <c r="I45" s="21">
-        <v>1</v>
-      </c>
-      <c r="J45" s="21">
-        <v>0</v>
-      </c>
-      <c r="K45" s="21">
-        <v>0</v>
-      </c>
-      <c r="L45" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="M45" s="35"/>
-      <c r="N45" s="35" t="s">
+      <c r="B45" s="18">
+        <v>1</v>
+      </c>
+      <c r="C45" s="18">
+        <v>1</v>
+      </c>
+      <c r="D45" s="18">
+        <v>1</v>
+      </c>
+      <c r="E45" s="18">
+        <v>1</v>
+      </c>
+      <c r="F45" s="18">
+        <v>1</v>
+      </c>
+      <c r="G45" s="18">
+        <v>1</v>
+      </c>
+      <c r="H45" s="18">
+        <v>0</v>
+      </c>
+      <c r="I45" s="18">
+        <v>1</v>
+      </c>
+      <c r="J45" s="18">
+        <v>0</v>
+      </c>
+      <c r="K45" s="18">
+        <v>0</v>
+      </c>
+      <c r="L45" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="M45" s="49"/>
+      <c r="N45" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="O45" s="35"/>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="35"/>
-      <c r="R45" s="42"/>
+      <c r="O45" s="49"/>
+      <c r="P45" s="49"/>
+      <c r="Q45" s="49"/>
+      <c r="R45" s="79"/>
       <c r="T45" s="4">
         <f t="shared" si="2"/>
         <v>64768</v>
@@ -5557,52 +5671,52 @@
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="8">
-        <v>1</v>
-      </c>
-      <c r="C46" s="8">
-        <v>1</v>
-      </c>
-      <c r="D46" s="8">
-        <v>1</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1</v>
-      </c>
-      <c r="F46" s="8">
-        <v>1</v>
-      </c>
-      <c r="G46" s="8">
-        <v>1</v>
-      </c>
-      <c r="H46" s="8">
-        <v>0</v>
-      </c>
-      <c r="I46" s="8">
-        <v>1</v>
-      </c>
-      <c r="J46" s="8">
-        <v>0</v>
-      </c>
-      <c r="K46" s="8">
-        <v>1</v>
-      </c>
-      <c r="L46" s="15">
-        <v>0</v>
-      </c>
-      <c r="M46" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="N46" s="32" t="s">
+      <c r="B46" s="7">
+        <v>1</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1</v>
+      </c>
+      <c r="F46" s="7">
+        <v>1</v>
+      </c>
+      <c r="G46" s="7">
+        <v>1</v>
+      </c>
+      <c r="H46" s="7">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7">
+        <v>1</v>
+      </c>
+      <c r="J46" s="7">
+        <v>0</v>
+      </c>
+      <c r="K46" s="7">
+        <v>1</v>
+      </c>
+      <c r="L46" s="13">
+        <v>0</v>
+      </c>
+      <c r="M46" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="N46" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="O46" s="32"/>
-      <c r="P46" s="32"/>
-      <c r="Q46" s="40"/>
-      <c r="R46" s="48" t="s">
+      <c r="O46" s="46"/>
+      <c r="P46" s="46"/>
+      <c r="Q46" s="54"/>
+      <c r="R46" s="68" t="s">
         <v>57</v>
       </c>
       <c r="T46" s="4">
@@ -5647,7 +5761,7 @@
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="38" t="s">
         <v>29</v>
       </c>
       <c r="B47" s="5">
@@ -5680,19 +5794,19 @@
       <c r="K47" s="5">
         <v>1</v>
       </c>
-      <c r="L47" s="17">
-        <v>1</v>
-      </c>
-      <c r="M47" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N47" s="28" t="s">
+      <c r="L47" s="15">
+        <v>1</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N47" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O47" s="28"/>
-      <c r="P47" s="28"/>
-      <c r="Q47" s="39"/>
-      <c r="R47" s="49"/>
+      <c r="O47" s="42"/>
+      <c r="P47" s="42"/>
+      <c r="Q47" s="53"/>
+      <c r="R47" s="69"/>
       <c r="T47" s="4">
         <f t="shared" si="2"/>
         <v>64864</v>
@@ -5735,7 +5849,7 @@
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="38" t="s">
         <v>19</v>
       </c>
       <c r="B48" s="5">
@@ -5768,19 +5882,19 @@
       <c r="K48" s="5">
         <v>0</v>
       </c>
-      <c r="L48" s="17">
-        <v>0</v>
-      </c>
-      <c r="M48" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N48" s="28" t="s">
+      <c r="L48" s="15">
+        <v>0</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N48" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O48" s="28"/>
-      <c r="P48" s="28"/>
-      <c r="Q48" s="39"/>
-      <c r="R48" s="49"/>
+      <c r="O48" s="42"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="69"/>
       <c r="T48" s="4">
         <f t="shared" si="2"/>
         <v>64896</v>
@@ -5823,7 +5937,7 @@
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="38" t="s">
         <v>20</v>
       </c>
       <c r="B49" s="5">
@@ -5856,19 +5970,19 @@
       <c r="K49" s="5">
         <v>0</v>
       </c>
-      <c r="L49" s="17">
-        <v>1</v>
-      </c>
-      <c r="M49" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N49" s="28" t="s">
+      <c r="L49" s="15">
+        <v>1</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N49" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="39"/>
-      <c r="R49" s="49"/>
+      <c r="O49" s="42"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="53"/>
+      <c r="R49" s="69"/>
       <c r="T49" s="4">
         <f t="shared" si="2"/>
         <v>64928</v>
@@ -5911,7 +6025,7 @@
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="38" t="s">
         <v>21</v>
       </c>
       <c r="B50" s="5">
@@ -5944,19 +6058,19 @@
       <c r="K50" s="5">
         <v>1</v>
       </c>
-      <c r="L50" s="17">
-        <v>0</v>
-      </c>
-      <c r="M50" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N50" s="28" t="s">
+      <c r="L50" s="15">
+        <v>0</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N50" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O50" s="28"/>
-      <c r="P50" s="28"/>
-      <c r="Q50" s="39"/>
-      <c r="R50" s="49"/>
+      <c r="O50" s="42"/>
+      <c r="P50" s="42"/>
+      <c r="Q50" s="53"/>
+      <c r="R50" s="69"/>
       <c r="T50" s="4">
         <f t="shared" si="2"/>
         <v>64960</v>
@@ -5999,7 +6113,7 @@
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="38" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="5">
@@ -6032,19 +6146,19 @@
       <c r="K51" s="5">
         <v>1</v>
       </c>
-      <c r="L51" s="17">
-        <v>1</v>
-      </c>
-      <c r="M51" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N51" s="28" t="s">
+      <c r="L51" s="15">
+        <v>1</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N51" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="39"/>
-      <c r="R51" s="49"/>
+      <c r="O51" s="42"/>
+      <c r="P51" s="42"/>
+      <c r="Q51" s="53"/>
+      <c r="R51" s="69"/>
       <c r="T51" s="4">
         <f t="shared" si="2"/>
         <v>64992</v>
@@ -6087,8 +6201,8 @@
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
-        <v>139</v>
+      <c r="A52" s="38" t="s">
+        <v>138</v>
       </c>
       <c r="B52" s="5">
         <v>1</v>
@@ -6120,19 +6234,19 @@
       <c r="K52" s="5">
         <v>0</v>
       </c>
-      <c r="L52" s="17">
-        <v>0</v>
-      </c>
-      <c r="M52" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N52" s="28" t="s">
+      <c r="L52" s="15">
+        <v>0</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N52" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="49"/>
+      <c r="O52" s="42"/>
+      <c r="P52" s="42"/>
+      <c r="Q52" s="53"/>
+      <c r="R52" s="69"/>
       <c r="T52" s="4">
         <f t="shared" si="2"/>
         <v>65024</v>
@@ -6175,8 +6289,8 @@
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
-        <v>140</v>
+      <c r="A53" s="38" t="s">
+        <v>139</v>
       </c>
       <c r="B53" s="5">
         <v>1</v>
@@ -6208,19 +6322,19 @@
       <c r="K53" s="5">
         <v>0</v>
       </c>
-      <c r="L53" s="17">
-        <v>1</v>
-      </c>
-      <c r="M53" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N53" s="28" t="s">
+      <c r="L53" s="15">
+        <v>1</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N53" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
-      <c r="Q53" s="39"/>
-      <c r="R53" s="49"/>
+      <c r="O53" s="42"/>
+      <c r="P53" s="42"/>
+      <c r="Q53" s="53"/>
+      <c r="R53" s="69"/>
       <c r="T53" s="4">
         <f t="shared" si="2"/>
         <v>65056</v>
@@ -6263,7 +6377,7 @@
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="38" t="s">
         <v>23</v>
       </c>
       <c r="B54" s="5">
@@ -6296,19 +6410,19 @@
       <c r="K54" s="5">
         <v>1</v>
       </c>
-      <c r="L54" s="17">
-        <v>0</v>
-      </c>
-      <c r="M54" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N54" s="28" t="s">
+      <c r="L54" s="15">
+        <v>0</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N54" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O54" s="28"/>
-      <c r="P54" s="28"/>
-      <c r="Q54" s="39"/>
-      <c r="R54" s="49"/>
+      <c r="O54" s="42"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="53"/>
+      <c r="R54" s="69"/>
       <c r="T54" s="4">
         <f t="shared" si="2"/>
         <v>65088</v>
@@ -6351,7 +6465,7 @@
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="38" t="s">
         <v>24</v>
       </c>
       <c r="B55" s="5">
@@ -6384,19 +6498,19 @@
       <c r="K55" s="5">
         <v>1</v>
       </c>
-      <c r="L55" s="17">
-        <v>1</v>
-      </c>
-      <c r="M55" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N55" s="28" t="s">
+      <c r="L55" s="15">
+        <v>1</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N55" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="39"/>
-      <c r="R55" s="49"/>
+      <c r="O55" s="42"/>
+      <c r="P55" s="42"/>
+      <c r="Q55" s="53"/>
+      <c r="R55" s="69"/>
       <c r="T55" s="4">
         <f t="shared" si="2"/>
         <v>65120</v>
@@ -6439,7 +6553,7 @@
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="38" t="s">
         <v>25</v>
       </c>
       <c r="B56" s="5">
@@ -6472,19 +6586,19 @@
       <c r="K56" s="5">
         <v>0</v>
       </c>
-      <c r="L56" s="17">
-        <v>0</v>
-      </c>
-      <c r="M56" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N56" s="28" t="s">
+      <c r="L56" s="15">
+        <v>0</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N56" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O56" s="28"/>
-      <c r="P56" s="28"/>
-      <c r="Q56" s="39"/>
-      <c r="R56" s="49"/>
+      <c r="O56" s="42"/>
+      <c r="P56" s="42"/>
+      <c r="Q56" s="53"/>
+      <c r="R56" s="69"/>
       <c r="T56" s="4">
         <f t="shared" si="2"/>
         <v>65152</v>
@@ -6527,7 +6641,7 @@
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="38" t="s">
         <v>26</v>
       </c>
       <c r="B57" s="5">
@@ -6560,19 +6674,19 @@
       <c r="K57" s="5">
         <v>0</v>
       </c>
-      <c r="L57" s="17">
-        <v>1</v>
-      </c>
-      <c r="M57" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N57" s="28" t="s">
+      <c r="L57" s="15">
+        <v>1</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N57" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O57" s="28"/>
-      <c r="P57" s="28"/>
-      <c r="Q57" s="39"/>
-      <c r="R57" s="49"/>
+      <c r="O57" s="42"/>
+      <c r="P57" s="42"/>
+      <c r="Q57" s="53"/>
+      <c r="R57" s="69"/>
       <c r="T57" s="4">
         <f t="shared" si="2"/>
         <v>65184</v>
@@ -6615,8 +6729,8 @@
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
-        <v>129</v>
+      <c r="A58" s="38" t="s">
+        <v>128</v>
       </c>
       <c r="B58" s="5">
         <v>1</v>
@@ -6648,19 +6762,19 @@
       <c r="K58" s="5">
         <v>1</v>
       </c>
-      <c r="L58" s="17">
-        <v>0</v>
-      </c>
-      <c r="M58" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N58" s="28" t="s">
+      <c r="L58" s="15">
+        <v>0</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="N58" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="39"/>
-      <c r="R58" s="49"/>
+      <c r="O58" s="42"/>
+      <c r="P58" s="42"/>
+      <c r="Q58" s="53"/>
+      <c r="R58" s="69"/>
       <c r="T58" s="4">
         <f t="shared" si="2"/>
         <v>65216</v>
@@ -6703,8 +6817,8 @@
       </c>
     </row>
     <row r="59" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
-        <v>150</v>
+      <c r="A59" s="38" t="s">
+        <v>149</v>
       </c>
       <c r="B59" s="5">
         <v>1</v>
@@ -6736,19 +6850,19 @@
       <c r="K59" s="5">
         <v>1</v>
       </c>
-      <c r="L59" s="17">
-        <v>1</v>
-      </c>
-      <c r="M59" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="N59" s="29" t="s">
+      <c r="L59" s="15">
+        <v>1</v>
+      </c>
+      <c r="M59" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="N59" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="O59" s="29"/>
-      <c r="P59" s="29"/>
-      <c r="Q59" s="42"/>
-      <c r="R59" s="49"/>
+      <c r="O59" s="43"/>
+      <c r="P59" s="43"/>
+      <c r="Q59" s="56"/>
+      <c r="R59" s="69"/>
       <c r="T59" s="4">
         <f t="shared" ref="T59:T61" si="21">U59*$E$19+V59*$I$19+W59*$M$19+X59</f>
         <v>65248</v>
@@ -6791,52 +6905,52 @@
       </c>
     </row>
     <row r="60" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B60" s="11">
-        <v>1</v>
-      </c>
-      <c r="C60" s="11">
-        <v>1</v>
-      </c>
-      <c r="D60" s="11">
-        <v>1</v>
-      </c>
-      <c r="E60" s="11">
-        <v>1</v>
-      </c>
-      <c r="F60" s="11">
-        <v>1</v>
-      </c>
-      <c r="G60" s="11">
-        <v>1</v>
-      </c>
-      <c r="H60" s="11">
-        <v>1</v>
-      </c>
-      <c r="I60" s="11">
-        <v>1</v>
-      </c>
-      <c r="J60" s="11">
-        <v>0</v>
-      </c>
-      <c r="K60" s="11">
-        <v>0</v>
-      </c>
-      <c r="L60" s="16">
-        <v>0</v>
-      </c>
-      <c r="M60" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="N60" s="29" t="s">
+      <c r="A60" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" s="9">
+        <v>1</v>
+      </c>
+      <c r="C60" s="9">
+        <v>1</v>
+      </c>
+      <c r="D60" s="9">
+        <v>1</v>
+      </c>
+      <c r="E60" s="9">
+        <v>1</v>
+      </c>
+      <c r="F60" s="9">
+        <v>1</v>
+      </c>
+      <c r="G60" s="9">
+        <v>1</v>
+      </c>
+      <c r="H60" s="9">
+        <v>1</v>
+      </c>
+      <c r="I60" s="9">
+        <v>1</v>
+      </c>
+      <c r="J60" s="9">
+        <v>0</v>
+      </c>
+      <c r="K60" s="9">
+        <v>0</v>
+      </c>
+      <c r="L60" s="14">
+        <v>0</v>
+      </c>
+      <c r="M60" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="N60" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="O60" s="29"/>
-      <c r="P60" s="29"/>
-      <c r="Q60" s="42"/>
-      <c r="R60" s="50"/>
+      <c r="O60" s="43"/>
+      <c r="P60" s="43"/>
+      <c r="Q60" s="56"/>
+      <c r="R60" s="70"/>
       <c r="T60" s="4">
         <f t="shared" si="21"/>
         <v>65280</v>
@@ -6879,58 +6993,58 @@
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61" s="23">
-        <v>1</v>
-      </c>
-      <c r="C61" s="23">
-        <v>1</v>
-      </c>
-      <c r="D61" s="23">
-        <v>1</v>
-      </c>
-      <c r="E61" s="23">
-        <v>1</v>
-      </c>
-      <c r="F61" s="23">
-        <v>1</v>
-      </c>
-      <c r="G61" s="23">
-        <v>1</v>
-      </c>
-      <c r="H61" s="23">
-        <v>1</v>
-      </c>
-      <c r="I61" s="23">
-        <v>1</v>
-      </c>
-      <c r="J61" s="23">
-        <v>0</v>
-      </c>
-      <c r="K61" s="23">
-        <v>0</v>
-      </c>
-      <c r="L61" s="23">
-        <v>1</v>
-      </c>
-      <c r="M61" s="23">
-        <v>0</v>
-      </c>
-      <c r="N61" s="23">
-        <v>0</v>
-      </c>
-      <c r="O61" s="23">
-        <v>0</v>
-      </c>
-      <c r="P61" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="24">
-        <v>0</v>
-      </c>
-      <c r="R61" s="43" t="s">
+      <c r="A61" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B61" s="20">
+        <v>1</v>
+      </c>
+      <c r="C61" s="20">
+        <v>1</v>
+      </c>
+      <c r="D61" s="20">
+        <v>1</v>
+      </c>
+      <c r="E61" s="20">
+        <v>1</v>
+      </c>
+      <c r="F61" s="20">
+        <v>1</v>
+      </c>
+      <c r="G61" s="20">
+        <v>1</v>
+      </c>
+      <c r="H61" s="20">
+        <v>1</v>
+      </c>
+      <c r="I61" s="20">
+        <v>1</v>
+      </c>
+      <c r="J61" s="20">
+        <v>0</v>
+      </c>
+      <c r="K61" s="20">
+        <v>0</v>
+      </c>
+      <c r="L61" s="20">
+        <v>1</v>
+      </c>
+      <c r="M61" s="20">
+        <v>0</v>
+      </c>
+      <c r="N61" s="20">
+        <v>0</v>
+      </c>
+      <c r="O61" s="20">
+        <v>0</v>
+      </c>
+      <c r="P61" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="21">
+        <v>0</v>
+      </c>
+      <c r="R61" s="63" t="s">
         <v>58</v>
       </c>
       <c r="T61" s="4">
@@ -6975,27 +7089,27 @@
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A62" s="51" t="str">
+      <c r="A62" s="71" t="str">
         <f>T63-T61 &amp; " Address reserved"</f>
-        <v>211 Address reserved</v>
-      </c>
-      <c r="B62" s="52"/>
-      <c r="C62" s="52"/>
-      <c r="D62" s="52"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="52"/>
-      <c r="G62" s="52"/>
-      <c r="H62" s="52"/>
-      <c r="I62" s="52"/>
-      <c r="J62" s="52"/>
-      <c r="K62" s="52"/>
-      <c r="L62" s="52"/>
-      <c r="M62" s="52"/>
-      <c r="N62" s="52"/>
-      <c r="O62" s="52"/>
-      <c r="P62" s="52"/>
-      <c r="Q62" s="53"/>
-      <c r="R62" s="44"/>
+        <v>208 Address reserved</v>
+      </c>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="72"/>
+      <c r="G62" s="72"/>
+      <c r="H62" s="72"/>
+      <c r="I62" s="72"/>
+      <c r="J62" s="72"/>
+      <c r="K62" s="72"/>
+      <c r="L62" s="72"/>
+      <c r="M62" s="72"/>
+      <c r="N62" s="72"/>
+      <c r="O62" s="72"/>
+      <c r="P62" s="72"/>
+      <c r="Q62" s="73"/>
+      <c r="R62" s="64"/>
       <c r="T62" s="4"/>
       <c r="U62" s="5"/>
       <c r="V62" s="5"/>
@@ -7008,8 +7122,8 @@
       <c r="AC62" s="4"/>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
-        <v>63</v>
+      <c r="A63" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="B63" s="5">
         <v>1</v>
@@ -7054,18 +7168,18 @@
         <v>0</v>
       </c>
       <c r="P63" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="17">
-        <v>1</v>
-      </c>
-      <c r="R63" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q63" s="15">
+        <v>0</v>
+      </c>
+      <c r="R63" s="64"/>
       <c r="T63" s="4">
         <f t="shared" ref="T63" si="31">U63*$E$19+V63*$I$19+W63*$M$19+X63</f>
-        <v>65523</v>
+        <v>65520</v>
       </c>
       <c r="U63" s="5">
-        <f t="shared" ref="U63:U64" si="32">IF(OR(E63=0,E63=1),E63,0)+IF(OR(D63=0,D63=1),D63*2,0)+IF(OR(C63=0,C63=1),C63*4,0)+IF(OR(B63=0,B63=1),B63*8,0)</f>
+        <f t="shared" ref="U63" si="32">IF(OR(E63=0,E63=1),E63,0)+IF(OR(D63=0,D63=1),D63*2,0)+IF(OR(C63=0,C63=1),C63*4,0)+IF(OR(B63=0,B63=1),B63*8,0)</f>
         <v>15</v>
       </c>
       <c r="V63" s="5">
@@ -7078,10 +7192,10 @@
       </c>
       <c r="X63" s="5">
         <f>IF(OR(Q63=0,Q63=1),Q63,0)+IF(OR(P63=0,P63=1),P63*2,0)+IF(OR(O63=0,O63=1),O63*4,0)+IF(OR(N63=0,N63=1),N63*8,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y63" s="5" t="str">
-        <f t="shared" ref="Y63:Y64" si="35">IF(U63&lt;10,U63,MID("ABCDEF",U63-9,1))</f>
+        <f t="shared" ref="Y63" si="35">IF(U63&lt;10,U63,MID("ABCDEF",U63-9,1))</f>
         <v>F</v>
       </c>
       <c r="Z63" s="5" t="str">
@@ -7094,578 +7208,580 @@
       </c>
       <c r="AB63" s="5">
         <f t="shared" ref="AB63" si="38">IF(X63&lt;10,X63,MID("ABCDEF",X63-9,1))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC63" s="4" t="str">
         <f t="shared" ref="AC63" si="39">Y63 &amp; Z63 &amp; AA63 &amp; AB63</f>
+        <v>FFF0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A64" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B64" s="5">
+        <v>1</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1</v>
+      </c>
+      <c r="D64" s="5">
+        <v>1</v>
+      </c>
+      <c r="E64" s="5">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5">
+        <v>1</v>
+      </c>
+      <c r="H64" s="5">
+        <v>1</v>
+      </c>
+      <c r="I64" s="5">
+        <v>1</v>
+      </c>
+      <c r="J64" s="5">
+        <v>1</v>
+      </c>
+      <c r="K64" s="5">
+        <v>1</v>
+      </c>
+      <c r="L64" s="5">
+        <v>1</v>
+      </c>
+      <c r="M64" s="5">
+        <v>1</v>
+      </c>
+      <c r="N64" s="5">
+        <v>0</v>
+      </c>
+      <c r="O64" s="5">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="15">
+        <v>1</v>
+      </c>
+      <c r="R64" s="64"/>
+      <c r="T64" s="4">
+        <f t="shared" ref="T64:T67" si="40">U64*$E$19+V64*$I$19+W64*$M$19+X64</f>
+        <v>65521</v>
+      </c>
+      <c r="U64" s="5">
+        <f t="shared" ref="U64:U67" si="41">IF(OR(E64=0,E64=1),E64,0)+IF(OR(D64=0,D64=1),D64*2,0)+IF(OR(C64=0,C64=1),C64*4,0)+IF(OR(B64=0,B64=1),B64*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="V64" s="5">
+        <f t="shared" ref="V64:V67" si="42">IF(OR(I64=0,I64=1),I64,0)+IF(OR(H64=0,H64=1),H64*2,0)+IF(OR(G64=0,G64=1),G64*4,0)+IF(OR(F64=0,F64=1),F64*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="W64" s="5">
+        <f t="shared" ref="W64:W67" si="43">IF(OR(M64=0,M64=1),M64,0)+IF(OR(L64=0,L64=1),L64*2,0)+IF(OR(K64=0,K64=1),K64*4,0)+IF(OR(J64=0,J64=1),J64*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="X64" s="5">
+        <f t="shared" ref="X64:X67" si="44">IF(OR(Q64=0,Q64=1),Q64,0)+IF(OR(P64=0,P64=1),P64*2,0)+IF(OR(O64=0,O64=1),O64*4,0)+IF(OR(N64=0,N64=1),N64*8,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y64" s="5" t="str">
+        <f t="shared" ref="Y64:Y67" si="45">IF(U64&lt;10,U64,MID("ABCDEF",U64-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="Z64" s="5" t="str">
+        <f t="shared" ref="Z64:Z67" si="46">IF(V64&lt;10,V64,MID("ABCDEF",V64-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="AA64" s="5" t="str">
+        <f t="shared" ref="AA64:AA67" si="47">IF(W64&lt;10,W64,MID("ABCDEF",W64-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="AB64" s="5">
+        <f t="shared" ref="AB64:AB67" si="48">IF(X64&lt;10,X64,MID("ABCDEF",X64-9,1))</f>
+        <v>1</v>
+      </c>
+      <c r="AC64" s="4" t="str">
+        <f t="shared" ref="AC64:AC67" si="49">Y64 &amp; Z64 &amp; AA64 &amp; AB64</f>
+        <v>FFF1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A65" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" s="5">
+        <v>1</v>
+      </c>
+      <c r="C65" s="5">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5">
+        <v>1</v>
+      </c>
+      <c r="F65" s="5">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5">
+        <v>1</v>
+      </c>
+      <c r="H65" s="5">
+        <v>1</v>
+      </c>
+      <c r="I65" s="5">
+        <v>1</v>
+      </c>
+      <c r="J65" s="5">
+        <v>1</v>
+      </c>
+      <c r="K65" s="5">
+        <v>1</v>
+      </c>
+      <c r="L65" s="5">
+        <v>1</v>
+      </c>
+      <c r="M65" s="5">
+        <v>1</v>
+      </c>
+      <c r="N65" s="5">
+        <v>0</v>
+      </c>
+      <c r="O65" s="5">
+        <v>0</v>
+      </c>
+      <c r="P65" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="15">
+        <v>0</v>
+      </c>
+      <c r="R65" s="64"/>
+      <c r="T65" s="4">
+        <f t="shared" si="40"/>
+        <v>65522</v>
+      </c>
+      <c r="U65" s="5">
+        <f t="shared" si="41"/>
+        <v>15</v>
+      </c>
+      <c r="V65" s="5">
+        <f t="shared" si="42"/>
+        <v>15</v>
+      </c>
+      <c r="W65" s="5">
+        <f t="shared" si="43"/>
+        <v>15</v>
+      </c>
+      <c r="X65" s="5">
+        <f t="shared" si="44"/>
+        <v>2</v>
+      </c>
+      <c r="Y65" s="5" t="str">
+        <f t="shared" si="45"/>
+        <v>F</v>
+      </c>
+      <c r="Z65" s="5" t="str">
+        <f t="shared" si="46"/>
+        <v>F</v>
+      </c>
+      <c r="AA65" s="5" t="str">
+        <f t="shared" si="47"/>
+        <v>F</v>
+      </c>
+      <c r="AB65" s="5">
+        <f t="shared" si="48"/>
+        <v>2</v>
+      </c>
+      <c r="AC65" s="4" t="str">
+        <f t="shared" si="49"/>
+        <v>FFF2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A66" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="B66" s="5">
+        <v>1</v>
+      </c>
+      <c r="C66" s="5">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5">
+        <v>1</v>
+      </c>
+      <c r="E66" s="5">
+        <v>1</v>
+      </c>
+      <c r="F66" s="5">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5">
+        <v>1</v>
+      </c>
+      <c r="H66" s="5">
+        <v>1</v>
+      </c>
+      <c r="I66" s="5">
+        <v>1</v>
+      </c>
+      <c r="J66" s="5">
+        <v>1</v>
+      </c>
+      <c r="K66" s="5">
+        <v>1</v>
+      </c>
+      <c r="L66" s="5">
+        <v>1</v>
+      </c>
+      <c r="M66" s="5">
+        <v>1</v>
+      </c>
+      <c r="N66" s="5">
+        <v>0</v>
+      </c>
+      <c r="O66" s="5">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="15">
+        <v>1</v>
+      </c>
+      <c r="R66" s="64"/>
+      <c r="T66" s="4">
+        <f t="shared" si="40"/>
+        <v>65523</v>
+      </c>
+      <c r="U66" s="5">
+        <f t="shared" si="41"/>
+        <v>15</v>
+      </c>
+      <c r="V66" s="5">
+        <f t="shared" si="42"/>
+        <v>15</v>
+      </c>
+      <c r="W66" s="5">
+        <f t="shared" si="43"/>
+        <v>15</v>
+      </c>
+      <c r="X66" s="5">
+        <f t="shared" si="44"/>
+        <v>3</v>
+      </c>
+      <c r="Y66" s="5" t="str">
+        <f t="shared" si="45"/>
+        <v>F</v>
+      </c>
+      <c r="Z66" s="5" t="str">
+        <f t="shared" si="46"/>
+        <v>F</v>
+      </c>
+      <c r="AA66" s="5" t="str">
+        <f t="shared" si="47"/>
+        <v>F</v>
+      </c>
+      <c r="AB66" s="5">
+        <f t="shared" si="48"/>
+        <v>3</v>
+      </c>
+      <c r="AC66" s="4" t="str">
+        <f t="shared" si="49"/>
         <v>FFF3</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B64" s="5">
-        <v>1</v>
-      </c>
-      <c r="C64" s="5">
-        <v>1</v>
-      </c>
-      <c r="D64" s="5">
-        <v>1</v>
-      </c>
-      <c r="E64" s="5">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5">
-        <v>1</v>
-      </c>
-      <c r="H64" s="5">
-        <v>1</v>
-      </c>
-      <c r="I64" s="5">
-        <v>1</v>
-      </c>
-      <c r="J64" s="5">
-        <v>1</v>
-      </c>
-      <c r="K64" s="5">
-        <v>1</v>
-      </c>
-      <c r="L64" s="5">
-        <v>1</v>
-      </c>
-      <c r="M64" s="5">
-        <v>1</v>
-      </c>
-      <c r="N64" s="5">
-        <v>0</v>
-      </c>
-      <c r="O64" s="5">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="17">
-        <v>0</v>
-      </c>
-      <c r="R64" s="44"/>
-      <c r="T64" s="4">
-        <f t="shared" ref="T64" si="40">U64*$E$19+V64*$I$19+W64*$M$19+X64</f>
-        <v>63472</v>
-      </c>
-      <c r="U64" s="5">
-        <f t="shared" ref="U64" si="41">IF(OR(E64=0,E64=1),E64,0)+IF(OR(D64=0,D64=1),D64*2,0)+IF(OR(C64=0,C64=1),C64*4,0)+IF(OR(B64=0,B64=1),B64*8,0)</f>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A67" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="5">
+        <v>1</v>
+      </c>
+      <c r="C67" s="5">
+        <v>1</v>
+      </c>
+      <c r="D67" s="5">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5">
+        <v>1</v>
+      </c>
+      <c r="H67" s="5">
+        <v>1</v>
+      </c>
+      <c r="I67" s="5">
+        <v>1</v>
+      </c>
+      <c r="J67" s="5">
+        <v>1</v>
+      </c>
+      <c r="K67" s="5">
+        <v>1</v>
+      </c>
+      <c r="L67" s="5">
+        <v>1</v>
+      </c>
+      <c r="M67" s="5">
+        <v>1</v>
+      </c>
+      <c r="N67" s="5">
+        <v>0</v>
+      </c>
+      <c r="O67" s="5">
+        <v>1</v>
+      </c>
+      <c r="P67" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="15">
+        <v>0</v>
+      </c>
+      <c r="R67" s="64"/>
+      <c r="T67" s="4">
+        <f t="shared" si="40"/>
+        <v>65524</v>
+      </c>
+      <c r="U67" s="5">
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
-      <c r="V64" s="5">
-        <f t="shared" ref="V64" si="42">IF(OR(I64=0,I64=1),I64,0)+IF(OR(H64=0,H64=1),H64*2,0)+IF(OR(G64=0,G64=1),G64*4,0)+IF(OR(F64=0,F64=1),F64*8,0)</f>
-        <v>7</v>
-      </c>
-      <c r="W64" s="5">
-        <f t="shared" ref="W64" si="43">IF(OR(M64=0,M64=1),M64,0)+IF(OR(L64=0,L64=1),L64*2,0)+IF(OR(K64=0,K64=1),K64*4,0)+IF(OR(J64=0,J64=1),J64*8,0)</f>
+      <c r="V67" s="5">
+        <f t="shared" si="42"/>
         <v>15</v>
       </c>
-      <c r="X64" s="5">
-        <f>IF(OR(Q64=0,Q64=1),Q64,0)+IF(OR(P64=0,P64=1),P64*2,0)+IF(OR(O64=0,O64=1),O64*4,0)+IF(OR(N64=0,N64=1),N64*8,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y64" s="5" t="str">
-        <f t="shared" ref="Y64" si="44">IF(U64&lt;10,U64,MID("ABCDEF",U64-9,1))</f>
+      <c r="W67" s="5">
+        <f t="shared" si="43"/>
+        <v>15</v>
+      </c>
+      <c r="X67" s="5">
+        <f t="shared" si="44"/>
+        <v>4</v>
+      </c>
+      <c r="Y67" s="5" t="str">
+        <f t="shared" si="45"/>
         <v>F</v>
       </c>
-      <c r="Z64" s="5">
-        <f t="shared" ref="Z64" si="45">IF(V64&lt;10,V64,MID("ABCDEF",V64-9,1))</f>
-        <v>7</v>
-      </c>
-      <c r="AA64" s="5" t="str">
-        <f t="shared" ref="AA64" si="46">IF(W64&lt;10,W64,MID("ABCDEF",W64-9,1))</f>
+      <c r="Z67" s="5" t="str">
+        <f t="shared" si="46"/>
         <v>F</v>
       </c>
-      <c r="AB64" s="5">
-        <f t="shared" ref="AB64" si="47">IF(X64&lt;10,X64,MID("ABCDEF",X64-9,1))</f>
-        <v>0</v>
-      </c>
-      <c r="AC64" s="4" t="str">
-        <f t="shared" ref="AC64" si="48">Y64 &amp; Z64 &amp; AA64 &amp; AB64</f>
-        <v>F7F0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B65" s="5">
-        <v>1</v>
-      </c>
-      <c r="C65" s="5">
-        <v>1</v>
-      </c>
-      <c r="D65" s="5">
-        <v>1</v>
-      </c>
-      <c r="E65" s="5">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5">
-        <v>1</v>
-      </c>
-      <c r="G65" s="5">
-        <v>1</v>
-      </c>
-      <c r="H65" s="5">
-        <v>1</v>
-      </c>
-      <c r="I65" s="5">
-        <v>1</v>
-      </c>
-      <c r="J65" s="5">
-        <v>1</v>
-      </c>
-      <c r="K65" s="5">
-        <v>1</v>
-      </c>
-      <c r="L65" s="5">
-        <v>1</v>
-      </c>
-      <c r="M65" s="5">
-        <v>1</v>
-      </c>
-      <c r="N65" s="5">
-        <v>0</v>
-      </c>
-      <c r="O65" s="5">
-        <v>0</v>
-      </c>
-      <c r="P65" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="17">
-        <v>1</v>
-      </c>
-      <c r="R65" s="44"/>
-      <c r="T65" s="4">
-        <f t="shared" ref="T65:T68" si="49">U65*$E$19+V65*$I$19+W65*$M$19+X65</f>
-        <v>65521</v>
-      </c>
-      <c r="U65" s="5">
-        <f t="shared" ref="U65:U68" si="50">IF(OR(E65=0,E65=1),E65,0)+IF(OR(D65=0,D65=1),D65*2,0)+IF(OR(C65=0,C65=1),C65*4,0)+IF(OR(B65=0,B65=1),B65*8,0)</f>
+      <c r="AA67" s="5" t="str">
+        <f t="shared" si="47"/>
+        <v>F</v>
+      </c>
+      <c r="AB67" s="5">
+        <f t="shared" si="48"/>
+        <v>4</v>
+      </c>
+      <c r="AC67" s="4" t="str">
+        <f t="shared" si="49"/>
+        <v>FFF4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A68" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" s="5">
+        <v>1</v>
+      </c>
+      <c r="C68" s="5">
+        <v>1</v>
+      </c>
+      <c r="D68" s="5">
+        <v>1</v>
+      </c>
+      <c r="E68" s="5">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5">
+        <v>1</v>
+      </c>
+      <c r="H68" s="5">
+        <v>1</v>
+      </c>
+      <c r="I68" s="5">
+        <v>1</v>
+      </c>
+      <c r="J68" s="5">
+        <v>1</v>
+      </c>
+      <c r="K68" s="5">
+        <v>1</v>
+      </c>
+      <c r="L68" s="5">
+        <v>1</v>
+      </c>
+      <c r="M68" s="5">
+        <v>1</v>
+      </c>
+      <c r="N68" s="5">
+        <v>0</v>
+      </c>
+      <c r="O68" s="5">
+        <v>1</v>
+      </c>
+      <c r="P68" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="15">
+        <v>1</v>
+      </c>
+      <c r="R68" s="64"/>
+      <c r="T68" s="4">
+        <f t="shared" ref="T68" si="50">U68*$E$19+V68*$I$19+W68*$M$19+X68</f>
+        <v>65525</v>
+      </c>
+      <c r="U68" s="5">
+        <f t="shared" ref="U68" si="51">IF(OR(E68=0,E68=1),E68,0)+IF(OR(D68=0,D68=1),D68*2,0)+IF(OR(C68=0,C68=1),C68*4,0)+IF(OR(B68=0,B68=1),B68*8,0)</f>
         <v>15</v>
       </c>
-      <c r="V65" s="5">
-        <f t="shared" ref="V65:V68" si="51">IF(OR(I65=0,I65=1),I65,0)+IF(OR(H65=0,H65=1),H65*2,0)+IF(OR(G65=0,G65=1),G65*4,0)+IF(OR(F65=0,F65=1),F65*8,0)</f>
+      <c r="V68" s="5">
+        <f t="shared" ref="V68" si="52">IF(OR(I68=0,I68=1),I68,0)+IF(OR(H68=0,H68=1),H68*2,0)+IF(OR(G68=0,G68=1),G68*4,0)+IF(OR(F68=0,F68=1),F68*8,0)</f>
         <v>15</v>
       </c>
-      <c r="W65" s="5">
-        <f t="shared" ref="W65:W68" si="52">IF(OR(M65=0,M65=1),M65,0)+IF(OR(L65=0,L65=1),L65*2,0)+IF(OR(K65=0,K65=1),K65*4,0)+IF(OR(J65=0,J65=1),J65*8,0)</f>
+      <c r="W68" s="5">
+        <f t="shared" ref="W68" si="53">IF(OR(M68=0,M68=1),M68,0)+IF(OR(L68=0,L68=1),L68*2,0)+IF(OR(K68=0,K68=1),K68*4,0)+IF(OR(J68=0,J68=1),J68*8,0)</f>
         <v>15</v>
       </c>
-      <c r="X65" s="5">
-        <f t="shared" ref="X65:X68" si="53">IF(OR(Q65=0,Q65=1),Q65,0)+IF(OR(P65=0,P65=1),P65*2,0)+IF(OR(O65=0,O65=1),O65*4,0)+IF(OR(N65=0,N65=1),N65*8,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Y65" s="5" t="str">
-        <f t="shared" ref="Y65:Y68" si="54">IF(U65&lt;10,U65,MID("ABCDEF",U65-9,1))</f>
+      <c r="X68" s="5">
+        <f>IF(OR(Q68=0,Q68=1),Q68,0)+IF(OR(P68=0,P68=1),P68*2,0)+IF(OR(O68=0,O68=1),O68*4,0)+IF(OR(N68=0,N68=1),N68*8,0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y68" s="5" t="str">
+        <f t="shared" ref="Y68" si="54">IF(U68&lt;10,U68,MID("ABCDEF",U68-9,1))</f>
         <v>F</v>
       </c>
-      <c r="Z65" s="5" t="str">
-        <f t="shared" ref="Z65:Z68" si="55">IF(V65&lt;10,V65,MID("ABCDEF",V65-9,1))</f>
+      <c r="Z68" s="5" t="str">
+        <f t="shared" ref="Z68" si="55">IF(V68&lt;10,V68,MID("ABCDEF",V68-9,1))</f>
         <v>F</v>
       </c>
-      <c r="AA65" s="5" t="str">
-        <f t="shared" ref="AA65:AA68" si="56">IF(W65&lt;10,W65,MID("ABCDEF",W65-9,1))</f>
+      <c r="AA68" s="5" t="str">
+        <f t="shared" ref="AA68" si="56">IF(W68&lt;10,W68,MID("ABCDEF",W68-9,1))</f>
         <v>F</v>
       </c>
-      <c r="AB65" s="5">
-        <f t="shared" ref="AB65:AB68" si="57">IF(X65&lt;10,X65,MID("ABCDEF",X65-9,1))</f>
-        <v>1</v>
-      </c>
-      <c r="AC65" s="4" t="str">
-        <f t="shared" ref="AC65:AC68" si="58">Y65 &amp; Z65 &amp; AA65 &amp; AB65</f>
-        <v>FFF1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="B66" s="5">
-        <v>1</v>
-      </c>
-      <c r="C66" s="5">
-        <v>1</v>
-      </c>
-      <c r="D66" s="5">
-        <v>1</v>
-      </c>
-      <c r="E66" s="5">
-        <v>1</v>
-      </c>
-      <c r="F66" s="5">
-        <v>1</v>
-      </c>
-      <c r="G66" s="5">
-        <v>1</v>
-      </c>
-      <c r="H66" s="5">
-        <v>1</v>
-      </c>
-      <c r="I66" s="5">
-        <v>1</v>
-      </c>
-      <c r="J66" s="5">
-        <v>1</v>
-      </c>
-      <c r="K66" s="5">
-        <v>1</v>
-      </c>
-      <c r="L66" s="5">
-        <v>1</v>
-      </c>
-      <c r="M66" s="5">
-        <v>1</v>
-      </c>
-      <c r="N66" s="5">
-        <v>0</v>
-      </c>
-      <c r="O66" s="5">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q66" s="17">
-        <v>0</v>
-      </c>
-      <c r="R66" s="44"/>
-      <c r="T66" s="4">
-        <f t="shared" si="49"/>
-        <v>65522</v>
-      </c>
-      <c r="U66" s="5">
-        <f t="shared" si="50"/>
+      <c r="AB68" s="5">
+        <f t="shared" ref="AB68" si="57">IF(X68&lt;10,X68,MID("ABCDEF",X68-9,1))</f>
+        <v>5</v>
+      </c>
+      <c r="AC68" s="4" t="str">
+        <f t="shared" ref="AC68" si="58">Y68 &amp; Z68 &amp; AA68 &amp; AB68</f>
+        <v>FFF5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A69" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="5">
+        <v>1</v>
+      </c>
+      <c r="C69" s="5">
+        <v>1</v>
+      </c>
+      <c r="D69" s="5">
+        <v>1</v>
+      </c>
+      <c r="E69" s="5">
+        <v>1</v>
+      </c>
+      <c r="F69" s="5">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5">
+        <v>1</v>
+      </c>
+      <c r="H69" s="5">
+        <v>1</v>
+      </c>
+      <c r="I69" s="5">
+        <v>1</v>
+      </c>
+      <c r="J69" s="5">
+        <v>1</v>
+      </c>
+      <c r="K69" s="5">
+        <v>1</v>
+      </c>
+      <c r="L69" s="5">
+        <v>1</v>
+      </c>
+      <c r="M69" s="5">
+        <v>1</v>
+      </c>
+      <c r="N69" s="5">
+        <v>0</v>
+      </c>
+      <c r="O69" s="5">
+        <v>1</v>
+      </c>
+      <c r="P69" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="15">
+        <v>0</v>
+      </c>
+      <c r="R69" s="64"/>
+      <c r="T69" s="4">
+        <f t="shared" si="2"/>
+        <v>65526</v>
+      </c>
+      <c r="U69" s="5">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="V66" s="5">
-        <f t="shared" si="51"/>
+      <c r="V69" s="5">
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="W66" s="5">
-        <f t="shared" si="52"/>
+      <c r="W69" s="5">
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="X66" s="5">
-        <f t="shared" si="53"/>
-        <v>2</v>
-      </c>
-      <c r="Y66" s="5" t="str">
-        <f t="shared" si="54"/>
+      <c r="X69" s="5">
+        <f t="shared" ref="X69:X78" si="59">IF(OR(Q69=0,Q69=1),Q69,0)+IF(OR(P69=0,P69=1),P69*2,0)+IF(OR(O69=0,O69=1),O69*4,0)+IF(OR(N69=0,N69=1),N69*8,0)</f>
+        <v>6</v>
+      </c>
+      <c r="Y69" s="5" t="str">
+        <f t="shared" si="6"/>
         <v>F</v>
       </c>
-      <c r="Z66" s="5" t="str">
-        <f t="shared" si="55"/>
+      <c r="Z69" s="5" t="str">
+        <f t="shared" si="7"/>
         <v>F</v>
       </c>
-      <c r="AA66" s="5" t="str">
-        <f t="shared" si="56"/>
+      <c r="AA69" s="5" t="str">
+        <f t="shared" si="8"/>
         <v>F</v>
       </c>
-      <c r="AB66" s="5">
-        <f t="shared" si="57"/>
-        <v>2</v>
-      </c>
-      <c r="AC66" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>FFF2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B67" s="5">
-        <v>1</v>
-      </c>
-      <c r="C67" s="5">
-        <v>1</v>
-      </c>
-      <c r="D67" s="5">
-        <v>1</v>
-      </c>
-      <c r="E67" s="5">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5">
-        <v>1</v>
-      </c>
-      <c r="G67" s="5">
-        <v>1</v>
-      </c>
-      <c r="H67" s="5">
-        <v>1</v>
-      </c>
-      <c r="I67" s="5">
-        <v>1</v>
-      </c>
-      <c r="J67" s="5">
-        <v>1</v>
-      </c>
-      <c r="K67" s="5">
-        <v>1</v>
-      </c>
-      <c r="L67" s="5">
-        <v>1</v>
-      </c>
-      <c r="M67" s="5">
-        <v>1</v>
-      </c>
-      <c r="N67" s="5">
-        <v>0</v>
-      </c>
-      <c r="O67" s="5">
-        <v>0</v>
-      </c>
-      <c r="P67" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="17">
-        <v>1</v>
-      </c>
-      <c r="R67" s="44"/>
-      <c r="T67" s="4">
-        <f t="shared" si="49"/>
-        <v>65523</v>
-      </c>
-      <c r="U67" s="5">
-        <f t="shared" si="50"/>
-        <v>15</v>
-      </c>
-      <c r="V67" s="5">
-        <f t="shared" si="51"/>
-        <v>15</v>
-      </c>
-      <c r="W67" s="5">
-        <f t="shared" si="52"/>
-        <v>15</v>
-      </c>
-      <c r="X67" s="5">
-        <f t="shared" si="53"/>
-        <v>3</v>
-      </c>
-      <c r="Y67" s="5" t="str">
-        <f t="shared" si="54"/>
-        <v>F</v>
-      </c>
-      <c r="Z67" s="5" t="str">
-        <f t="shared" si="55"/>
-        <v>F</v>
-      </c>
-      <c r="AA67" s="5" t="str">
-        <f t="shared" si="56"/>
-        <v>F</v>
-      </c>
-      <c r="AB67" s="5">
-        <f t="shared" si="57"/>
-        <v>3</v>
-      </c>
-      <c r="AC67" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>FFF3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" s="5">
-        <v>1</v>
-      </c>
-      <c r="C68" s="5">
-        <v>1</v>
-      </c>
-      <c r="D68" s="5">
-        <v>1</v>
-      </c>
-      <c r="E68" s="5">
-        <v>1</v>
-      </c>
-      <c r="F68" s="5">
-        <v>1</v>
-      </c>
-      <c r="G68" s="5">
-        <v>1</v>
-      </c>
-      <c r="H68" s="5">
-        <v>1</v>
-      </c>
-      <c r="I68" s="5">
-        <v>1</v>
-      </c>
-      <c r="J68" s="5">
-        <v>1</v>
-      </c>
-      <c r="K68" s="5">
-        <v>1</v>
-      </c>
-      <c r="L68" s="5">
-        <v>1</v>
-      </c>
-      <c r="M68" s="5">
-        <v>1</v>
-      </c>
-      <c r="N68" s="5">
-        <v>0</v>
-      </c>
-      <c r="O68" s="5">
-        <v>1</v>
-      </c>
-      <c r="P68" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="17">
-        <v>0</v>
-      </c>
-      <c r="R68" s="44"/>
-      <c r="T68" s="4">
-        <f t="shared" si="49"/>
-        <v>65524</v>
-      </c>
-      <c r="U68" s="5">
-        <f t="shared" si="50"/>
-        <v>15</v>
-      </c>
-      <c r="V68" s="5">
-        <f t="shared" si="51"/>
-        <v>15</v>
-      </c>
-      <c r="W68" s="5">
-        <f t="shared" si="52"/>
-        <v>15</v>
-      </c>
-      <c r="X68" s="5">
-        <f t="shared" si="53"/>
-        <v>4</v>
-      </c>
-      <c r="Y68" s="5" t="str">
-        <f t="shared" si="54"/>
-        <v>F</v>
-      </c>
-      <c r="Z68" s="5" t="str">
-        <f t="shared" si="55"/>
-        <v>F</v>
-      </c>
-      <c r="AA68" s="5" t="str">
-        <f t="shared" si="56"/>
-        <v>F</v>
-      </c>
-      <c r="AB68" s="5">
-        <f t="shared" si="57"/>
-        <v>4</v>
-      </c>
-      <c r="AC68" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>FFF4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B69" s="5">
-        <v>1</v>
-      </c>
-      <c r="C69" s="5">
-        <v>1</v>
-      </c>
-      <c r="D69" s="5">
-        <v>1</v>
-      </c>
-      <c r="E69" s="5">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5">
-        <v>1</v>
-      </c>
-      <c r="G69" s="5">
-        <v>1</v>
-      </c>
-      <c r="H69" s="5">
-        <v>1</v>
-      </c>
-      <c r="I69" s="5">
-        <v>1</v>
-      </c>
-      <c r="J69" s="5">
-        <v>1</v>
-      </c>
-      <c r="K69" s="5">
-        <v>1</v>
-      </c>
-      <c r="L69" s="5">
-        <v>1</v>
-      </c>
-      <c r="M69" s="5">
-        <v>1</v>
-      </c>
-      <c r="N69" s="5">
-        <v>0</v>
-      </c>
-      <c r="O69" s="5">
-        <v>1</v>
-      </c>
-      <c r="P69" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="17">
-        <v>1</v>
-      </c>
-      <c r="R69" s="44"/>
-      <c r="T69" s="4">
-        <f t="shared" ref="T69" si="59">U69*$E$19+V69*$I$19+W69*$M$19+X69</f>
-        <v>65525</v>
-      </c>
-      <c r="U69" s="5">
-        <f t="shared" ref="U69" si="60">IF(OR(E69=0,E69=1),E69,0)+IF(OR(D69=0,D69=1),D69*2,0)+IF(OR(C69=0,C69=1),C69*4,0)+IF(OR(B69=0,B69=1),B69*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="V69" s="5">
-        <f t="shared" ref="V69" si="61">IF(OR(I69=0,I69=1),I69,0)+IF(OR(H69=0,H69=1),H69*2,0)+IF(OR(G69=0,G69=1),G69*4,0)+IF(OR(F69=0,F69=1),F69*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="W69" s="5">
-        <f t="shared" ref="W69" si="62">IF(OR(M69=0,M69=1),M69,0)+IF(OR(L69=0,L69=1),L69*2,0)+IF(OR(K69=0,K69=1),K69*4,0)+IF(OR(J69=0,J69=1),J69*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="X69" s="5">
-        <f>IF(OR(Q69=0,Q69=1),Q69,0)+IF(OR(P69=0,P69=1),P69*2,0)+IF(OR(O69=0,O69=1),O69*4,0)+IF(OR(N69=0,N69=1),N69*8,0)</f>
-        <v>5</v>
-      </c>
-      <c r="Y69" s="5" t="str">
-        <f t="shared" ref="Y69" si="63">IF(U69&lt;10,U69,MID("ABCDEF",U69-9,1))</f>
-        <v>F</v>
-      </c>
-      <c r="Z69" s="5" t="str">
-        <f t="shared" ref="Z69" si="64">IF(V69&lt;10,V69,MID("ABCDEF",V69-9,1))</f>
-        <v>F</v>
-      </c>
-      <c r="AA69" s="5" t="str">
-        <f t="shared" ref="AA69" si="65">IF(W69&lt;10,W69,MID("ABCDEF",W69-9,1))</f>
-        <v>F</v>
-      </c>
       <c r="AB69" s="5">
-        <f t="shared" ref="AB69" si="66">IF(X69&lt;10,X69,MID("ABCDEF",X69-9,1))</f>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>6</v>
       </c>
       <c r="AC69" s="4" t="str">
-        <f t="shared" ref="AC69" si="67">Y69 &amp; Z69 &amp; AA69 &amp; AB69</f>
-        <v>FFF5</v>
+        <f t="shared" si="10"/>
+        <v>FFF6</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
-        <v>153</v>
+      <c r="A70" s="40" t="s">
+        <v>135</v>
       </c>
       <c r="B70" s="5">
         <v>1</v>
@@ -7712,13 +7828,13 @@
       <c r="P70" s="5">
         <v>1</v>
       </c>
-      <c r="Q70" s="17">
-        <v>0</v>
-      </c>
-      <c r="R70" s="44"/>
+      <c r="Q70" s="15">
+        <v>1</v>
+      </c>
+      <c r="R70" s="64"/>
       <c r="T70" s="4">
         <f t="shared" si="2"/>
-        <v>65526</v>
+        <v>65527</v>
       </c>
       <c r="U70" s="5">
         <f t="shared" si="3"/>
@@ -7733,8 +7849,8 @@
         <v>15</v>
       </c>
       <c r="X70" s="5">
-        <f t="shared" ref="X70:X79" si="68">IF(OR(Q70=0,Q70=1),Q70,0)+IF(OR(P70=0,P70=1),P70*2,0)+IF(OR(O70=0,O70=1),O70*4,0)+IF(OR(N70=0,N70=1),N70*8,0)</f>
-        <v>6</v>
+        <f t="shared" si="59"/>
+        <v>7</v>
       </c>
       <c r="Y70" s="5" t="str">
         <f t="shared" si="6"/>
@@ -7750,16 +7866,16 @@
       </c>
       <c r="AB70" s="5">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC70" s="4" t="str">
         <f t="shared" si="10"/>
-        <v>FFF6</v>
+        <v>FFF7</v>
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
-        <v>136</v>
+      <c r="A71" s="40" t="s">
+        <v>134</v>
       </c>
       <c r="B71" s="5">
         <v>1</v>
@@ -7798,21 +7914,21 @@
         <v>1</v>
       </c>
       <c r="N71" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="17">
-        <v>1</v>
-      </c>
-      <c r="R71" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q71" s="15">
+        <v>0</v>
+      </c>
+      <c r="R71" s="64"/>
       <c r="T71" s="4">
         <f t="shared" si="2"/>
-        <v>65527</v>
+        <v>65528</v>
       </c>
       <c r="U71" s="5">
         <f t="shared" si="3"/>
@@ -7827,8 +7943,8 @@
         <v>15</v>
       </c>
       <c r="X71" s="5">
-        <f t="shared" si="68"/>
-        <v>7</v>
+        <f t="shared" si="59"/>
+        <v>8</v>
       </c>
       <c r="Y71" s="5" t="str">
         <f t="shared" si="6"/>
@@ -7844,16 +7960,16 @@
       </c>
       <c r="AB71" s="5">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC71" s="4" t="str">
         <f t="shared" si="10"/>
-        <v>FFF7</v>
+        <v>FFF8</v>
       </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A72" s="9" t="s">
-        <v>135</v>
+      <c r="A72" s="40" t="s">
+        <v>62</v>
       </c>
       <c r="B72" s="5">
         <v>1</v>
@@ -7900,13 +8016,13 @@
       <c r="P72" s="5">
         <v>0</v>
       </c>
-      <c r="Q72" s="17">
-        <v>0</v>
-      </c>
-      <c r="R72" s="44"/>
+      <c r="Q72" s="15">
+        <v>1</v>
+      </c>
+      <c r="R72" s="64"/>
       <c r="T72" s="4">
         <f t="shared" si="2"/>
-        <v>65528</v>
+        <v>65529</v>
       </c>
       <c r="U72" s="5">
         <f t="shared" si="3"/>
@@ -7921,8 +8037,8 @@
         <v>15</v>
       </c>
       <c r="X72" s="5">
-        <f t="shared" si="68"/>
-        <v>8</v>
+        <f t="shared" si="59"/>
+        <v>9</v>
       </c>
       <c r="Y72" s="5" t="str">
         <f t="shared" si="6"/>
@@ -7938,16 +8054,16 @@
       </c>
       <c r="AB72" s="5">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC72" s="4" t="str">
         <f t="shared" si="10"/>
-        <v>FFF8</v>
+        <v>FFF9</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A73" s="9" t="s">
-        <v>62</v>
+      <c r="A73" s="40" t="s">
+        <v>132</v>
       </c>
       <c r="B73" s="5">
         <v>1</v>
@@ -7992,642 +8108,548 @@
         <v>0</v>
       </c>
       <c r="P73" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="17">
-        <v>1</v>
-      </c>
-      <c r="R73" s="44"/>
+        <v>1</v>
+      </c>
+      <c r="Q73" s="15">
+        <v>0</v>
+      </c>
+      <c r="R73" s="64"/>
       <c r="T73" s="4">
+        <f t="shared" ref="T73:T74" si="60">U73*$E$19+V73*$I$19+W73*$M$19+X73</f>
+        <v>65530</v>
+      </c>
+      <c r="U73" s="5">
+        <f t="shared" ref="U73:U74" si="61">IF(OR(E73=0,E73=1),E73,0)+IF(OR(D73=0,D73=1),D73*2,0)+IF(OR(C73=0,C73=1),C73*4,0)+IF(OR(B73=0,B73=1),B73*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="V73" s="5">
+        <f t="shared" ref="V73:V74" si="62">IF(OR(I73=0,I73=1),I73,0)+IF(OR(H73=0,H73=1),H73*2,0)+IF(OR(G73=0,G73=1),G73*4,0)+IF(OR(F73=0,F73=1),F73*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="W73" s="5">
+        <f t="shared" ref="W73:W74" si="63">IF(OR(M73=0,M73=1),M73,0)+IF(OR(L73=0,L73=1),L73*2,0)+IF(OR(K73=0,K73=1),K73*4,0)+IF(OR(J73=0,J73=1),J73*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="X73" s="5">
+        <f t="shared" si="59"/>
+        <v>10</v>
+      </c>
+      <c r="Y73" s="5" t="str">
+        <f t="shared" ref="Y73:Y74" si="64">IF(U73&lt;10,U73,MID("ABCDEF",U73-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="Z73" s="5" t="str">
+        <f t="shared" ref="Z73:Z74" si="65">IF(V73&lt;10,V73,MID("ABCDEF",V73-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="AA73" s="5" t="str">
+        <f t="shared" ref="AA73:AA74" si="66">IF(W73&lt;10,W73,MID("ABCDEF",W73-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="AB73" s="5" t="str">
+        <f t="shared" ref="AB73:AB74" si="67">IF(X73&lt;10,X73,MID("ABCDEF",X73-9,1))</f>
+        <v>A</v>
+      </c>
+      <c r="AC73" s="4" t="str">
+        <f t="shared" ref="AC73:AC74" si="68">Y73 &amp; Z73 &amp; AA73 &amp; AB73</f>
+        <v>FFFA</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A74" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="B74" s="5">
+        <v>1</v>
+      </c>
+      <c r="C74" s="5">
+        <v>1</v>
+      </c>
+      <c r="D74" s="5">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5">
+        <v>1</v>
+      </c>
+      <c r="G74" s="5">
+        <v>1</v>
+      </c>
+      <c r="H74" s="5">
+        <v>1</v>
+      </c>
+      <c r="I74" s="5">
+        <v>1</v>
+      </c>
+      <c r="J74" s="5">
+        <v>1</v>
+      </c>
+      <c r="K74" s="5">
+        <v>1</v>
+      </c>
+      <c r="L74" s="5">
+        <v>1</v>
+      </c>
+      <c r="M74" s="5">
+        <v>1</v>
+      </c>
+      <c r="N74" s="5">
+        <v>1</v>
+      </c>
+      <c r="O74" s="5">
+        <v>0</v>
+      </c>
+      <c r="P74" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="15">
+        <v>1</v>
+      </c>
+      <c r="R74" s="64"/>
+      <c r="T74" s="4">
+        <f t="shared" si="60"/>
+        <v>65531</v>
+      </c>
+      <c r="U74" s="5">
+        <f t="shared" si="61"/>
+        <v>15</v>
+      </c>
+      <c r="V74" s="5">
+        <f t="shared" si="62"/>
+        <v>15</v>
+      </c>
+      <c r="W74" s="5">
+        <f t="shared" si="63"/>
+        <v>15</v>
+      </c>
+      <c r="X74" s="5">
+        <f t="shared" si="59"/>
+        <v>11</v>
+      </c>
+      <c r="Y74" s="5" t="str">
+        <f t="shared" si="64"/>
+        <v>F</v>
+      </c>
+      <c r="Z74" s="5" t="str">
+        <f t="shared" si="65"/>
+        <v>F</v>
+      </c>
+      <c r="AA74" s="5" t="str">
+        <f t="shared" si="66"/>
+        <v>F</v>
+      </c>
+      <c r="AB74" s="5" t="str">
+        <f t="shared" si="67"/>
+        <v>B</v>
+      </c>
+      <c r="AC74" s="4" t="str">
+        <f t="shared" si="68"/>
+        <v>FFFB</v>
+      </c>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A75" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" s="5">
+        <v>1</v>
+      </c>
+      <c r="C75" s="5">
+        <v>1</v>
+      </c>
+      <c r="D75" s="5">
+        <v>1</v>
+      </c>
+      <c r="E75" s="5">
+        <v>1</v>
+      </c>
+      <c r="F75" s="5">
+        <v>1</v>
+      </c>
+      <c r="G75" s="5">
+        <v>1</v>
+      </c>
+      <c r="H75" s="5">
+        <v>1</v>
+      </c>
+      <c r="I75" s="5">
+        <v>1</v>
+      </c>
+      <c r="J75" s="5">
+        <v>1</v>
+      </c>
+      <c r="K75" s="5">
+        <v>1</v>
+      </c>
+      <c r="L75" s="5">
+        <v>1</v>
+      </c>
+      <c r="M75" s="5">
+        <v>1</v>
+      </c>
+      <c r="N75" s="5">
+        <v>1</v>
+      </c>
+      <c r="O75" s="5">
+        <v>1</v>
+      </c>
+      <c r="P75" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="15">
+        <v>0</v>
+      </c>
+      <c r="R75" s="64"/>
+      <c r="T75" s="4">
+        <f t="shared" ref="T75:T77" si="69">U75*$E$19+V75*$I$19+W75*$M$19+X75</f>
+        <v>65532</v>
+      </c>
+      <c r="U75" s="5">
+        <f t="shared" ref="U75:U77" si="70">IF(OR(E75=0,E75=1),E75,0)+IF(OR(D75=0,D75=1),D75*2,0)+IF(OR(C75=0,C75=1),C75*4,0)+IF(OR(B75=0,B75=1),B75*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="V75" s="5">
+        <f t="shared" ref="V75:V77" si="71">IF(OR(I75=0,I75=1),I75,0)+IF(OR(H75=0,H75=1),H75*2,0)+IF(OR(G75=0,G75=1),G75*4,0)+IF(OR(F75=0,F75=1),F75*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="W75" s="5">
+        <f t="shared" ref="W75:W77" si="72">IF(OR(M75=0,M75=1),M75,0)+IF(OR(L75=0,L75=1),L75*2,0)+IF(OR(K75=0,K75=1),K75*4,0)+IF(OR(J75=0,J75=1),J75*8,0)</f>
+        <v>15</v>
+      </c>
+      <c r="X75" s="5">
+        <f t="shared" ref="X75:X77" si="73">IF(OR(Q75=0,Q75=1),Q75,0)+IF(OR(P75=0,P75=1),P75*2,0)+IF(OR(O75=0,O75=1),O75*4,0)+IF(OR(N75=0,N75=1),N75*8,0)</f>
+        <v>12</v>
+      </c>
+      <c r="Y75" s="5" t="str">
+        <f t="shared" ref="Y75:Y77" si="74">IF(U75&lt;10,U75,MID("ABCDEF",U75-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="Z75" s="5" t="str">
+        <f t="shared" ref="Z75:Z77" si="75">IF(V75&lt;10,V75,MID("ABCDEF",V75-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="AA75" s="5" t="str">
+        <f t="shared" ref="AA75:AA77" si="76">IF(W75&lt;10,W75,MID("ABCDEF",W75-9,1))</f>
+        <v>F</v>
+      </c>
+      <c r="AB75" s="5" t="str">
+        <f t="shared" ref="AB75:AB77" si="77">IF(X75&lt;10,X75,MID("ABCDEF",X75-9,1))</f>
+        <v>C</v>
+      </c>
+      <c r="AC75" s="4" t="str">
+        <f t="shared" ref="AC75:AC77" si="78">Y75 &amp; Z75 &amp; AA75 &amp; AB75</f>
+        <v>FFFC</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A76" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76" s="5">
+        <v>1</v>
+      </c>
+      <c r="C76" s="5">
+        <v>1</v>
+      </c>
+      <c r="D76" s="5">
+        <v>1</v>
+      </c>
+      <c r="E76" s="5">
+        <v>1</v>
+      </c>
+      <c r="F76" s="5">
+        <v>1</v>
+      </c>
+      <c r="G76" s="5">
+        <v>1</v>
+      </c>
+      <c r="H76" s="5">
+        <v>1</v>
+      </c>
+      <c r="I76" s="5">
+        <v>1</v>
+      </c>
+      <c r="J76" s="5">
+        <v>1</v>
+      </c>
+      <c r="K76" s="5">
+        <v>1</v>
+      </c>
+      <c r="L76" s="5">
+        <v>1</v>
+      </c>
+      <c r="M76" s="5">
+        <v>1</v>
+      </c>
+      <c r="N76" s="5">
+        <v>1</v>
+      </c>
+      <c r="O76" s="5">
+        <v>1</v>
+      </c>
+      <c r="P76" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="15">
+        <v>1</v>
+      </c>
+      <c r="R76" s="64"/>
+      <c r="T76" s="4">
+        <f t="shared" si="69"/>
+        <v>65533</v>
+      </c>
+      <c r="U76" s="5">
+        <f t="shared" si="70"/>
+        <v>15</v>
+      </c>
+      <c r="V76" s="5">
+        <f t="shared" si="71"/>
+        <v>15</v>
+      </c>
+      <c r="W76" s="5">
+        <f t="shared" si="72"/>
+        <v>15</v>
+      </c>
+      <c r="X76" s="5">
+        <f t="shared" si="73"/>
+        <v>13</v>
+      </c>
+      <c r="Y76" s="5" t="str">
+        <f t="shared" si="74"/>
+        <v>F</v>
+      </c>
+      <c r="Z76" s="5" t="str">
+        <f t="shared" si="75"/>
+        <v>F</v>
+      </c>
+      <c r="AA76" s="5" t="str">
+        <f t="shared" si="76"/>
+        <v>F</v>
+      </c>
+      <c r="AB76" s="5" t="str">
+        <f t="shared" si="77"/>
+        <v>D</v>
+      </c>
+      <c r="AC76" s="4" t="str">
+        <f t="shared" si="78"/>
+        <v>FFFD</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A77" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77" s="5">
+        <v>1</v>
+      </c>
+      <c r="C77" s="5">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5">
+        <v>1</v>
+      </c>
+      <c r="F77" s="5">
+        <v>1</v>
+      </c>
+      <c r="G77" s="5">
+        <v>1</v>
+      </c>
+      <c r="H77" s="5">
+        <v>1</v>
+      </c>
+      <c r="I77" s="5">
+        <v>1</v>
+      </c>
+      <c r="J77" s="5">
+        <v>1</v>
+      </c>
+      <c r="K77" s="5">
+        <v>1</v>
+      </c>
+      <c r="L77" s="5">
+        <v>1</v>
+      </c>
+      <c r="M77" s="5">
+        <v>1</v>
+      </c>
+      <c r="N77" s="5">
+        <v>1</v>
+      </c>
+      <c r="O77" s="5">
+        <v>1</v>
+      </c>
+      <c r="P77" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="15">
+        <v>0</v>
+      </c>
+      <c r="R77" s="64"/>
+      <c r="T77" s="4">
+        <f t="shared" si="69"/>
+        <v>65534</v>
+      </c>
+      <c r="U77" s="5">
+        <f t="shared" si="70"/>
+        <v>15</v>
+      </c>
+      <c r="V77" s="5">
+        <f t="shared" si="71"/>
+        <v>15</v>
+      </c>
+      <c r="W77" s="5">
+        <f t="shared" si="72"/>
+        <v>15</v>
+      </c>
+      <c r="X77" s="5">
+        <f t="shared" si="73"/>
+        <v>14</v>
+      </c>
+      <c r="Y77" s="5" t="str">
+        <f t="shared" si="74"/>
+        <v>F</v>
+      </c>
+      <c r="Z77" s="5" t="str">
+        <f t="shared" si="75"/>
+        <v>F</v>
+      </c>
+      <c r="AA77" s="5" t="str">
+        <f t="shared" si="76"/>
+        <v>F</v>
+      </c>
+      <c r="AB77" s="5" t="str">
+        <f t="shared" si="77"/>
+        <v>E</v>
+      </c>
+      <c r="AC77" s="4" t="str">
+        <f t="shared" si="78"/>
+        <v>FFFE</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B78" s="9">
+        <v>1</v>
+      </c>
+      <c r="C78" s="9">
+        <v>1</v>
+      </c>
+      <c r="D78" s="9">
+        <v>1</v>
+      </c>
+      <c r="E78" s="9">
+        <v>1</v>
+      </c>
+      <c r="F78" s="9">
+        <v>1</v>
+      </c>
+      <c r="G78" s="9">
+        <v>1</v>
+      </c>
+      <c r="H78" s="9">
+        <v>1</v>
+      </c>
+      <c r="I78" s="9">
+        <v>1</v>
+      </c>
+      <c r="J78" s="9">
+        <v>1</v>
+      </c>
+      <c r="K78" s="9">
+        <v>1</v>
+      </c>
+      <c r="L78" s="9">
+        <v>1</v>
+      </c>
+      <c r="M78" s="9">
+        <v>1</v>
+      </c>
+      <c r="N78" s="9">
+        <v>1</v>
+      </c>
+      <c r="O78" s="9">
+        <v>1</v>
+      </c>
+      <c r="P78" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="14">
+        <v>1</v>
+      </c>
+      <c r="R78" s="65"/>
+      <c r="T78" s="4">
         <f t="shared" si="2"/>
-        <v>65529</v>
-      </c>
-      <c r="U73" s="5">
+        <v>65535</v>
+      </c>
+      <c r="U78" s="5">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="V73" s="5">
+      <c r="V78" s="5">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="W73" s="5">
+      <c r="W78" s="5">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="X73" s="5">
-        <f t="shared" si="68"/>
-        <v>9</v>
-      </c>
-      <c r="Y73" s="5" t="str">
+      <c r="X78" s="5">
+        <f t="shared" si="59"/>
+        <v>15</v>
+      </c>
+      <c r="Y78" s="5" t="str">
         <f t="shared" si="6"/>
         <v>F</v>
       </c>
-      <c r="Z73" s="5" t="str">
+      <c r="Z78" s="5" t="str">
         <f t="shared" si="7"/>
         <v>F</v>
       </c>
-      <c r="AA73" s="5" t="str">
+      <c r="AA78" s="5" t="str">
         <f t="shared" si="8"/>
         <v>F</v>
       </c>
-      <c r="AB73" s="5">
-        <f t="shared" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="AC73" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>FFF9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="B74" s="5">
-        <v>1</v>
-      </c>
-      <c r="C74" s="5">
-        <v>1</v>
-      </c>
-      <c r="D74" s="5">
-        <v>1</v>
-      </c>
-      <c r="E74" s="5">
-        <v>1</v>
-      </c>
-      <c r="F74" s="5">
-        <v>1</v>
-      </c>
-      <c r="G74" s="5">
-        <v>1</v>
-      </c>
-      <c r="H74" s="5">
-        <v>1</v>
-      </c>
-      <c r="I74" s="5">
-        <v>1</v>
-      </c>
-      <c r="J74" s="5">
-        <v>1</v>
-      </c>
-      <c r="K74" s="5">
-        <v>1</v>
-      </c>
-      <c r="L74" s="5">
-        <v>1</v>
-      </c>
-      <c r="M74" s="5">
-        <v>1</v>
-      </c>
-      <c r="N74" s="5">
-        <v>1</v>
-      </c>
-      <c r="O74" s="5">
-        <v>0</v>
-      </c>
-      <c r="P74" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q74" s="17">
-        <v>0</v>
-      </c>
-      <c r="R74" s="44"/>
-      <c r="T74" s="4">
-        <f t="shared" ref="T74:T75" si="69">U74*$E$19+V74*$I$19+W74*$M$19+X74</f>
-        <v>65530</v>
-      </c>
-      <c r="U74" s="5">
-        <f t="shared" ref="U74:U75" si="70">IF(OR(E74=0,E74=1),E74,0)+IF(OR(D74=0,D74=1),D74*2,0)+IF(OR(C74=0,C74=1),C74*4,0)+IF(OR(B74=0,B74=1),B74*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="V74" s="5">
-        <f t="shared" ref="V74:V75" si="71">IF(OR(I74=0,I74=1),I74,0)+IF(OR(H74=0,H74=1),H74*2,0)+IF(OR(G74=0,G74=1),G74*4,0)+IF(OR(F74=0,F74=1),F74*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="W74" s="5">
-        <f t="shared" ref="W74:W75" si="72">IF(OR(M74=0,M74=1),M74,0)+IF(OR(L74=0,L74=1),L74*2,0)+IF(OR(K74=0,K74=1),K74*4,0)+IF(OR(J74=0,J74=1),J74*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="X74" s="5">
-        <f t="shared" si="68"/>
-        <v>10</v>
-      </c>
-      <c r="Y74" s="5" t="str">
-        <f t="shared" ref="Y74:Y75" si="73">IF(U74&lt;10,U74,MID("ABCDEF",U74-9,1))</f>
-        <v>F</v>
-      </c>
-      <c r="Z74" s="5" t="str">
-        <f t="shared" ref="Z74:Z75" si="74">IF(V74&lt;10,V74,MID("ABCDEF",V74-9,1))</f>
-        <v>F</v>
-      </c>
-      <c r="AA74" s="5" t="str">
-        <f t="shared" ref="AA74:AA75" si="75">IF(W74&lt;10,W74,MID("ABCDEF",W74-9,1))</f>
-        <v>F</v>
-      </c>
-      <c r="AB74" s="5" t="str">
-        <f t="shared" ref="AB74:AB75" si="76">IF(X74&lt;10,X74,MID("ABCDEF",X74-9,1))</f>
-        <v>A</v>
-      </c>
-      <c r="AC74" s="4" t="str">
-        <f t="shared" ref="AC74:AC75" si="77">Y74 &amp; Z74 &amp; AA74 &amp; AB74</f>
-        <v>FFFA</v>
-      </c>
-    </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B75" s="5">
-        <v>1</v>
-      </c>
-      <c r="C75" s="5">
-        <v>1</v>
-      </c>
-      <c r="D75" s="5">
-        <v>1</v>
-      </c>
-      <c r="E75" s="5">
-        <v>1</v>
-      </c>
-      <c r="F75" s="5">
-        <v>1</v>
-      </c>
-      <c r="G75" s="5">
-        <v>1</v>
-      </c>
-      <c r="H75" s="5">
-        <v>1</v>
-      </c>
-      <c r="I75" s="5">
-        <v>1</v>
-      </c>
-      <c r="J75" s="5">
-        <v>1</v>
-      </c>
-      <c r="K75" s="5">
-        <v>1</v>
-      </c>
-      <c r="L75" s="5">
-        <v>1</v>
-      </c>
-      <c r="M75" s="5">
-        <v>1</v>
-      </c>
-      <c r="N75" s="5">
-        <v>1</v>
-      </c>
-      <c r="O75" s="5">
-        <v>0</v>
-      </c>
-      <c r="P75" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q75" s="17">
-        <v>1</v>
-      </c>
-      <c r="R75" s="44"/>
-      <c r="T75" s="4">
-        <f t="shared" si="69"/>
-        <v>65531</v>
-      </c>
-      <c r="U75" s="5">
-        <f t="shared" si="70"/>
-        <v>15</v>
-      </c>
-      <c r="V75" s="5">
-        <f t="shared" si="71"/>
-        <v>15</v>
-      </c>
-      <c r="W75" s="5">
-        <f t="shared" si="72"/>
-        <v>15</v>
-      </c>
-      <c r="X75" s="5">
-        <f t="shared" si="68"/>
-        <v>11</v>
-      </c>
-      <c r="Y75" s="5" t="str">
-        <f t="shared" si="73"/>
-        <v>F</v>
-      </c>
-      <c r="Z75" s="5" t="str">
-        <f t="shared" si="74"/>
-        <v>F</v>
-      </c>
-      <c r="AA75" s="5" t="str">
-        <f t="shared" si="75"/>
-        <v>F</v>
-      </c>
-      <c r="AB75" s="5" t="str">
-        <f t="shared" si="76"/>
-        <v>B</v>
-      </c>
-      <c r="AC75" s="4" t="str">
-        <f t="shared" si="77"/>
-        <v>FFFB</v>
-      </c>
-    </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B76" s="5">
-        <v>1</v>
-      </c>
-      <c r="C76" s="5">
-        <v>1</v>
-      </c>
-      <c r="D76" s="5">
-        <v>1</v>
-      </c>
-      <c r="E76" s="5">
-        <v>1</v>
-      </c>
-      <c r="F76" s="5">
-        <v>1</v>
-      </c>
-      <c r="G76" s="5">
-        <v>1</v>
-      </c>
-      <c r="H76" s="5">
-        <v>1</v>
-      </c>
-      <c r="I76" s="5">
-        <v>1</v>
-      </c>
-      <c r="J76" s="5">
-        <v>1</v>
-      </c>
-      <c r="K76" s="5">
-        <v>1</v>
-      </c>
-      <c r="L76" s="5">
-        <v>1</v>
-      </c>
-      <c r="M76" s="5">
-        <v>1</v>
-      </c>
-      <c r="N76" s="5">
-        <v>1</v>
-      </c>
-      <c r="O76" s="5">
-        <v>1</v>
-      </c>
-      <c r="P76" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="17">
-        <v>0</v>
-      </c>
-      <c r="R76" s="44"/>
-      <c r="T76" s="4">
-        <f t="shared" ref="T76:T78" si="78">U76*$E$19+V76*$I$19+W76*$M$19+X76</f>
-        <v>65532</v>
-      </c>
-      <c r="U76" s="5">
-        <f t="shared" ref="U76:U78" si="79">IF(OR(E76=0,E76=1),E76,0)+IF(OR(D76=0,D76=1),D76*2,0)+IF(OR(C76=0,C76=1),C76*4,0)+IF(OR(B76=0,B76=1),B76*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="V76" s="5">
-        <f t="shared" ref="V76:V78" si="80">IF(OR(I76=0,I76=1),I76,0)+IF(OR(H76=0,H76=1),H76*2,0)+IF(OR(G76=0,G76=1),G76*4,0)+IF(OR(F76=0,F76=1),F76*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="W76" s="5">
-        <f t="shared" ref="W76:W78" si="81">IF(OR(M76=0,M76=1),M76,0)+IF(OR(L76=0,L76=1),L76*2,0)+IF(OR(K76=0,K76=1),K76*4,0)+IF(OR(J76=0,J76=1),J76*8,0)</f>
-        <v>15</v>
-      </c>
-      <c r="X76" s="5">
-        <f t="shared" ref="X76:X78" si="82">IF(OR(Q76=0,Q76=1),Q76,0)+IF(OR(P76=0,P76=1),P76*2,0)+IF(OR(O76=0,O76=1),O76*4,0)+IF(OR(N76=0,N76=1),N76*8,0)</f>
-        <v>12</v>
-      </c>
-      <c r="Y76" s="5" t="str">
-        <f t="shared" ref="Y76:Y78" si="83">IF(U76&lt;10,U76,MID("ABCDEF",U76-9,1))</f>
-        <v>F</v>
-      </c>
-      <c r="Z76" s="5" t="str">
-        <f t="shared" ref="Z76:Z78" si="84">IF(V76&lt;10,V76,MID("ABCDEF",V76-9,1))</f>
-        <v>F</v>
-      </c>
-      <c r="AA76" s="5" t="str">
-        <f t="shared" ref="AA76:AA78" si="85">IF(W76&lt;10,W76,MID("ABCDEF",W76-9,1))</f>
-        <v>F</v>
-      </c>
-      <c r="AB76" s="5" t="str">
-        <f t="shared" ref="AB76:AB78" si="86">IF(X76&lt;10,X76,MID("ABCDEF",X76-9,1))</f>
-        <v>C</v>
-      </c>
-      <c r="AC76" s="4" t="str">
-        <f t="shared" ref="AC76:AC78" si="87">Y76 &amp; Z76 &amp; AA76 &amp; AB76</f>
-        <v>FFFC</v>
-      </c>
-    </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B77" s="5">
-        <v>1</v>
-      </c>
-      <c r="C77" s="5">
-        <v>1</v>
-      </c>
-      <c r="D77" s="5">
-        <v>1</v>
-      </c>
-      <c r="E77" s="5">
-        <v>1</v>
-      </c>
-      <c r="F77" s="5">
-        <v>1</v>
-      </c>
-      <c r="G77" s="5">
-        <v>1</v>
-      </c>
-      <c r="H77" s="5">
-        <v>1</v>
-      </c>
-      <c r="I77" s="5">
-        <v>1</v>
-      </c>
-      <c r="J77" s="5">
-        <v>1</v>
-      </c>
-      <c r="K77" s="5">
-        <v>1</v>
-      </c>
-      <c r="L77" s="5">
-        <v>1</v>
-      </c>
-      <c r="M77" s="5">
-        <v>1</v>
-      </c>
-      <c r="N77" s="5">
-        <v>1</v>
-      </c>
-      <c r="O77" s="5">
-        <v>1</v>
-      </c>
-      <c r="P77" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="17">
-        <v>1</v>
-      </c>
-      <c r="R77" s="44"/>
-      <c r="T77" s="4">
-        <f t="shared" si="78"/>
-        <v>65533</v>
-      </c>
-      <c r="U77" s="5">
-        <f t="shared" si="79"/>
-        <v>15</v>
-      </c>
-      <c r="V77" s="5">
-        <f t="shared" si="80"/>
-        <v>15</v>
-      </c>
-      <c r="W77" s="5">
-        <f t="shared" si="81"/>
-        <v>15</v>
-      </c>
-      <c r="X77" s="5">
-        <f t="shared" si="82"/>
-        <v>13</v>
-      </c>
-      <c r="Y77" s="5" t="str">
-        <f t="shared" si="83"/>
-        <v>F</v>
-      </c>
-      <c r="Z77" s="5" t="str">
-        <f t="shared" si="84"/>
-        <v>F</v>
-      </c>
-      <c r="AA77" s="5" t="str">
-        <f t="shared" si="85"/>
-        <v>F</v>
-      </c>
-      <c r="AB77" s="5" t="str">
-        <f t="shared" si="86"/>
-        <v>D</v>
-      </c>
-      <c r="AC77" s="4" t="str">
-        <f t="shared" si="87"/>
-        <v>FFFD</v>
-      </c>
-    </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B78" s="5">
-        <v>1</v>
-      </c>
-      <c r="C78" s="5">
-        <v>1</v>
-      </c>
-      <c r="D78" s="5">
-        <v>1</v>
-      </c>
-      <c r="E78" s="5">
-        <v>1</v>
-      </c>
-      <c r="F78" s="5">
-        <v>1</v>
-      </c>
-      <c r="G78" s="5">
-        <v>1</v>
-      </c>
-      <c r="H78" s="5">
-        <v>1</v>
-      </c>
-      <c r="I78" s="5">
-        <v>1</v>
-      </c>
-      <c r="J78" s="5">
-        <v>1</v>
-      </c>
-      <c r="K78" s="5">
-        <v>1</v>
-      </c>
-      <c r="L78" s="5">
-        <v>1</v>
-      </c>
-      <c r="M78" s="5">
-        <v>1</v>
-      </c>
-      <c r="N78" s="5">
-        <v>1</v>
-      </c>
-      <c r="O78" s="5">
-        <v>1</v>
-      </c>
-      <c r="P78" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q78" s="17">
-        <v>0</v>
-      </c>
-      <c r="R78" s="44"/>
-      <c r="T78" s="4">
-        <f t="shared" si="78"/>
-        <v>65534</v>
-      </c>
-      <c r="U78" s="5">
-        <f t="shared" si="79"/>
-        <v>15</v>
-      </c>
-      <c r="V78" s="5">
-        <f t="shared" si="80"/>
-        <v>15</v>
-      </c>
-      <c r="W78" s="5">
-        <f t="shared" si="81"/>
-        <v>15</v>
-      </c>
-      <c r="X78" s="5">
-        <f t="shared" si="82"/>
-        <v>14</v>
-      </c>
-      <c r="Y78" s="5" t="str">
-        <f t="shared" si="83"/>
-        <v>F</v>
-      </c>
-      <c r="Z78" s="5" t="str">
-        <f t="shared" si="84"/>
-        <v>F</v>
-      </c>
-      <c r="AA78" s="5" t="str">
-        <f t="shared" si="85"/>
-        <v>F</v>
-      </c>
       <c r="AB78" s="5" t="str">
-        <f t="shared" si="86"/>
-        <v>E</v>
-      </c>
-      <c r="AC78" s="4" t="str">
-        <f t="shared" si="87"/>
-        <v>FFFE</v>
-      </c>
-    </row>
-    <row r="79" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="11">
-        <v>1</v>
-      </c>
-      <c r="C79" s="11">
-        <v>1</v>
-      </c>
-      <c r="D79" s="11">
-        <v>1</v>
-      </c>
-      <c r="E79" s="11">
-        <v>1</v>
-      </c>
-      <c r="F79" s="11">
-        <v>1</v>
-      </c>
-      <c r="G79" s="11">
-        <v>1</v>
-      </c>
-      <c r="H79" s="11">
-        <v>1</v>
-      </c>
-      <c r="I79" s="11">
-        <v>1</v>
-      </c>
-      <c r="J79" s="11">
-        <v>1</v>
-      </c>
-      <c r="K79" s="11">
-        <v>1</v>
-      </c>
-      <c r="L79" s="11">
-        <v>1</v>
-      </c>
-      <c r="M79" s="11">
-        <v>1</v>
-      </c>
-      <c r="N79" s="11">
-        <v>1</v>
-      </c>
-      <c r="O79" s="11">
-        <v>1</v>
-      </c>
-      <c r="P79" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q79" s="16">
-        <v>1</v>
-      </c>
-      <c r="R79" s="45"/>
-      <c r="T79" s="4">
-        <f t="shared" si="2"/>
-        <v>65535</v>
-      </c>
-      <c r="U79" s="5">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V79" s="5">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="W79" s="5">
-        <f t="shared" si="5"/>
-        <v>15</v>
-      </c>
-      <c r="X79" s="5">
-        <f t="shared" si="68"/>
-        <v>15</v>
-      </c>
-      <c r="Y79" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>F</v>
-      </c>
-      <c r="Z79" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>F</v>
-      </c>
-      <c r="AA79" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>F</v>
-      </c>
-      <c r="AB79" s="5" t="str">
         <f t="shared" si="9"/>
         <v>F</v>
       </c>
-      <c r="AC79" s="4" t="str">
-        <f t="shared" ref="AC79" si="88">Y79 &amp; Z79 &amp; AA79 &amp; AB79</f>
+      <c r="AC78" s="4" t="str">
+        <f t="shared" ref="AC78" si="79">Y78 &amp; Z78 &amp; AA78 &amp; AB78</f>
         <v>FFFF</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="112">
     <mergeCell ref="N28:Q28"/>
     <mergeCell ref="T20:AC20"/>
     <mergeCell ref="N58:Q58"/>
-    <mergeCell ref="R61:R79"/>
+    <mergeCell ref="R61:R78"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="B7:K7"/>
@@ -8764,31 +8786,31 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="4">
         <v>0</v>
@@ -8796,31 +8818,31 @@
       <c r="C2" s="4">
         <v>8</v>
       </c>
-      <c r="D2" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="G2" s="57"/>
+      <c r="D2" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="80" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="81"/>
       <c r="H2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="46">
-        <v>0</v>
-      </c>
-      <c r="J2" s="58"/>
-      <c r="K2" s="47"/>
+        <v>64</v>
+      </c>
+      <c r="I2" s="66">
+        <v>0</v>
+      </c>
+      <c r="J2" s="82"/>
+      <c r="K2" s="67"/>
       <c r="L2" s="4">
         <v>1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
@@ -8828,29 +8850,29 @@
       <c r="C3" s="4">
         <v>8</v>
       </c>
-      <c r="D3" s="28"/>
-      <c r="F3" s="56" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="57"/>
+      <c r="D3" s="42"/>
+      <c r="F3" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="81"/>
       <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="80" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="83"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J3" s="59"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="M3" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" s="4">
         <v>2</v>
@@ -8858,29 +8880,29 @@
       <c r="C4" s="4">
         <v>16</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="F4" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="57"/>
+      <c r="D4" s="42"/>
+      <c r="F4" s="80" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="81"/>
       <c r="H4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="I4" s="80" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4" s="83"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="59"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="M4" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="4">
         <v>3</v>
@@ -8888,29 +8910,29 @@
       <c r="C5" s="4">
         <v>32</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="F5" s="56" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="57"/>
+      <c r="D5" s="42"/>
+      <c r="F5" s="80" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="81"/>
       <c r="H5" s="4">
         <v>2</v>
       </c>
-      <c r="I5" s="56" t="s">
+      <c r="I5" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" s="83"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="59"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="M5" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="4">
         <v>4</v>
@@ -8918,31 +8940,31 @@
       <c r="C6" s="4">
         <v>8</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="57"/>
+      <c r="D6" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="80" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="81"/>
       <c r="H6" s="4">
         <v>3</v>
       </c>
-      <c r="I6" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="J6" s="59"/>
-      <c r="K6" s="57"/>
+      <c r="I6" s="80" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" s="83"/>
+      <c r="K6" s="81"/>
       <c r="L6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="4">
         <v>5</v>
@@ -8950,29 +8972,29 @@
       <c r="C7" s="4">
         <v>8</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="F7" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="57"/>
+      <c r="D7" s="42"/>
+      <c r="F7" s="80" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="81"/>
       <c r="H7" s="4">
         <v>4</v>
       </c>
-      <c r="I7" s="56" t="s">
-        <v>274</v>
-      </c>
-      <c r="J7" s="59"/>
-      <c r="K7" s="57"/>
+      <c r="I7" s="80" t="s">
+        <v>273</v>
+      </c>
+      <c r="J7" s="83"/>
+      <c r="K7" s="81"/>
       <c r="L7" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" s="4">
         <v>6</v>
@@ -8980,29 +9002,29 @@
       <c r="C8" s="4">
         <v>16</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="F8" s="56" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="57"/>
+      <c r="D8" s="42"/>
+      <c r="F8" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="81"/>
       <c r="H8" s="4">
         <v>5</v>
       </c>
-      <c r="I8" s="56" t="s">
+      <c r="I8" s="80" t="s">
+        <v>111</v>
+      </c>
+      <c r="J8" s="83"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="59"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="M8" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="4">
         <v>7</v>
@@ -9010,29 +9032,29 @@
       <c r="C9" s="4">
         <v>32</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="F9" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="G9" s="57"/>
+      <c r="D9" s="42"/>
+      <c r="F9" s="80" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="81"/>
       <c r="H9" s="4">
         <v>6</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="59"/>
-      <c r="K9" s="57"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="81"/>
       <c r="L9" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="4">
         <v>8</v>
@@ -9041,30 +9063,30 @@
         <v>32</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="G10" s="57"/>
+        <v>97</v>
+      </c>
+      <c r="F10" s="80" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="81"/>
       <c r="H10" s="4">
         <v>7</v>
       </c>
-      <c r="I10" s="56" t="s">
+      <c r="I10" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" s="83"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J10" s="59"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="4">
         <v>9</v>
@@ -9073,12 +9095,12 @@
         <v>32</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4">
         <v>10</v>
@@ -9087,15 +9109,15 @@
         <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
+        <v>99</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -9108,23 +9130,23 @@
         <v>32</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="36"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="50"/>
       <c r="J13" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" s="4">
         <v>12</v>
@@ -9132,22 +9154,22 @@
       <c r="C14" s="4">
         <v>32</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="60"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="36" t="s">
+      <c r="D14" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="84"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="50"/>
+      <c r="J14" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" s="4">
         <v>13</v>
@@ -9155,18 +9177,18 @@
       <c r="C15" s="4">
         <v>32</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
+      <c r="D15" s="42"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="4">
         <v>14</v>
@@ -9174,18 +9196,18 @@
       <c r="C16" s="4">
         <v>32</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="F16" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
+      <c r="D16" s="42"/>
+      <c r="F16" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B17" s="4">
         <v>15</v>
@@ -9193,77 +9215,77 @@
       <c r="C17" s="4">
         <v>32</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="36" t="s">
+      <c r="D17" s="42"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="50"/>
+      <c r="J17" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="36"/>
-      <c r="J17" s="4" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="36"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="4">
         <v>8</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="62"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="50"/>
       <c r="C19" s="4">
         <v>32</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
+        <v>101</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="B20" s="36"/>
+      <c r="A20" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="B20" s="50"/>
       <c r="C20" s="4">
         <v>32</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="B21" s="36"/>
+      <c r="A21" s="50" t="s">
+        <v>275</v>
+      </c>
+      <c r="B21" s="50"/>
       <c r="C21" s="4">
         <v>32</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
